--- a/apps/portal/public/product_bulk_import_template.xlsx
+++ b/apps/portal/public/product_bulk_import_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uriel\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\School\DCDemo\DollysCloset-AdminAndEmployee\apps\portal\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1845FB3-3BD3-474B-AF0D-FE608FD5B4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17152E1A-7C51-4FCB-8F6B-87D68A49D690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="166">
   <si>
     <t>product_name</t>
   </si>
@@ -501,13 +501,46 @@
   </si>
   <si>
     <t>Cute casual dress for kids, fits ages 3-5</t>
+  </si>
+  <si>
+    <t>image_1</t>
+  </si>
+  <si>
+    <t>image_2</t>
+  </si>
+  <si>
+    <t>image_3</t>
+  </si>
+  <si>
+    <t>image_4</t>
+  </si>
+  <si>
+    <t>image_5</t>
+  </si>
+  <si>
+    <t>back.jpg</t>
+  </si>
+  <si>
+    <t>Second product image filename. Optional.</t>
+  </si>
+  <si>
+    <t>Third product image filename. Optional.</t>
+  </si>
+  <si>
+    <t>Fourth product image filename. Optional.</t>
+  </si>
+  <si>
+    <t>Fifth product image filename. Optional.</t>
+  </si>
+  <si>
+    <t>Filename of the primary (cover) photo for this product. e.g. front.jpg. Supported: jpg, jpeg, png, webp, gif, avif. Max 5 MB. If blank, the first filled image column is used as primary.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -547,6 +580,12 @@
       <sz val="11"/>
       <color rgb="FF4B5563"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -599,7 +638,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -608,10 +647,19 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -914,8 +962,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:D71"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B1:D76"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -923,14 +971,14 @@
     <col min="4" max="4" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="18" x14ac:dyDescent="0.4">
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+      <c r="B1" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
@@ -938,7 +986,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>0</v>
       </c>
@@ -946,7 +994,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
@@ -954,7 +1002,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>2</v>
       </c>
@@ -962,7 +1010,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>3</v>
       </c>
@@ -970,7 +1018,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>4</v>
       </c>
@@ -978,7 +1026,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>5</v>
       </c>
@@ -986,7 +1034,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>6</v>
       </c>
@@ -994,7 +1042,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>7</v>
       </c>
@@ -1002,7 +1050,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
@@ -1010,621 +1058,661 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="18" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+    <row r="13" spans="2:4" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B14" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B15" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B16" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B17" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+      <c r="B19" s="8" t="s">
         <v>21</v>
-      </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B15" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B16" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B17" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-    </row>
-    <row r="19" spans="2:4" ht="18" x14ac:dyDescent="0.4">
-      <c r="B19" s="6" t="s">
-        <v>25</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B20" s="1" t="s">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B20" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B21" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B22" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+    </row>
+    <row r="24" spans="2:4" ht="18" x14ac:dyDescent="0.25">
+      <c r="B24" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B21" s="2">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B26" s="2">
         <v>1</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C26" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B22" s="2">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B27" s="2">
         <v>2</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C27" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B23" s="2">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B28" s="2">
         <v>3</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C28" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B24" s="2">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B29" s="2">
         <v>4</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C29" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B25" s="2">
-        <v>5</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B26" s="2">
-        <v>6</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B27" s="2">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B28" s="2">
-        <v>8</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B29" s="2">
-        <v>9</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="2">
+        <v>5</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B31" s="2">
+        <v>6</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B32" s="2">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B33" s="2">
+        <v>8</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B34" s="2">
+        <v>9</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B35" s="2">
         <v>10</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B31" s="2">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B36" s="2">
         <v>11</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B32" s="2">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B37" s="2">
         <v>12</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C37" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B33" s="2">
-        <v>13</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B34" s="2">
-        <v>14</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B35" s="2">
-        <v>16</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B36" s="2">
-        <v>17</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B37" s="2">
-        <v>18</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B38" s="2">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B39" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B40" s="2">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B41" s="2">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B42" s="2">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B43" s="2">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" s="2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B45" s="2">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B46" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B47" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B48" s="2">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B49" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B50" s="2">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B51" s="2">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B52" s="2">
+        <v>28</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B53" s="2">
+        <v>29</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B54" s="2">
+        <v>30</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B55" s="2">
+        <v>31</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B56" s="2">
+        <v>32</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B57" s="2">
         <v>33</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C57" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D57" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="53" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B53" s="2">
+    <row r="58" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B58" s="2">
         <v>34</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C58" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D58" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="54" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B54" s="2">
+    <row r="59" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B59" s="2">
         <v>35</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C59" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="D59" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="55" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B55" s="2">
+    <row r="60" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B60" s="2">
         <v>36</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C60" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D60" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="56" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B56" s="2">
+    <row r="61" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B61" s="2">
         <v>37</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C61" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D61" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="57" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B57" s="2">
+    <row r="62" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B62" s="2">
         <v>38</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C62" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="58" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B58" s="2">
-        <v>39</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="59" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B59" s="2">
-        <v>40</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="60" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B60" s="2">
-        <v>41</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="61" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B61" s="2">
-        <v>42</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="62" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B62" s="2">
-        <v>43</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="63" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B63" s="2">
+        <v>39</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B64" s="2">
+        <v>40</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B65" s="2">
+        <v>41</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B66" s="2">
+        <v>42</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B67" s="2">
+        <v>43</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B68" s="2">
         <v>44</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C68" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D63" s="2" t="s">
+      <c r="D68" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="64" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B64" s="2">
+    <row r="69" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B69" s="2">
         <v>45</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C69" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="D69" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B65" s="2">
+    <row r="70" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B70" s="2">
         <v>46</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C70" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="D70" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B66" s="2">
+    <row r="71" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B71" s="2">
         <v>47</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C71" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D66" s="2" t="s">
+      <c r="D71" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="67" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B67" s="2">
+    <row r="72" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B72" s="2">
         <v>48</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C72" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="D72" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="68" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B68" s="2">
+    <row r="73" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B73" s="2">
         <v>49</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C73" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="D73" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="69" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B69" s="2">
+    <row r="74" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B74" s="2">
         <v>50</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C74" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="D74" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="70" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B70" s="2">
+    <row r="75" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B75" s="2">
         <v>51</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C75" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="D75" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="71" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B71" s="2">
+    <row r="76" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B76" s="2">
         <v>52</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C76" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="D76" s="2" t="s">
         <v>67</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B24:D24"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B14:D14"/>
     <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1632,50 +1720,66 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I101"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:N101"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="48" customWidth="1"/>
+    <col min="2" max="2" width="41.85546875" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="45" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="8" max="8" width="35.28515625" customWidth="1"/>
+    <col min="9" max="9" width="10.140625" customWidth="1"/>
+    <col min="10" max="14" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="10" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J1" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>141</v>
       </c>
@@ -1703,8 +1807,15 @@
       <c r="I2" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J2" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>146</v>
       </c>
@@ -1732,8 +1843,15 @@
       <c r="I3" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J3" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>150</v>
       </c>
@@ -1761,8 +1879,15 @@
       <c r="I4" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J4" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -1772,8 +1897,13 @@
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -1783,8 +1913,13 @@
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -1794,8 +1929,13 @@
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -1805,8 +1945,13 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -1816,8 +1961,13 @@
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -1827,8 +1977,13 @@
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -1838,8 +1993,13 @@
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -1849,8 +2009,13 @@
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -1860,8 +2025,13 @@
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -1871,8 +2041,13 @@
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -1882,8 +2057,13 @@
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -1893,8 +2073,13 @@
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -1904,8 +2089,13 @@
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -1915,8 +2105,13 @@
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
+      <c r="N18" s="4"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -1926,8 +2121,13 @@
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -1937,8 +2137,13 @@
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="4"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -1948,8 +2153,13 @@
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -1959,8 +2169,13 @@
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="4"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -1970,8 +2185,13 @@
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -1981,8 +2201,13 @@
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -1992,8 +2217,13 @@
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -2003,8 +2233,13 @@
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -2014,8 +2249,13 @@
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -2025,8 +2265,13 @@
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="4"/>
+      <c r="N28" s="4"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -2036,8 +2281,13 @@
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -2047,8 +2297,13 @@
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -2058,8 +2313,13 @@
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -2069,8 +2329,13 @@
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="4"/>
+      <c r="N32" s="4"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -2080,8 +2345,13 @@
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -2091,8 +2361,13 @@
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4"/>
+      <c r="N34" s="4"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -2102,8 +2377,13 @@
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -2113,8 +2393,13 @@
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J36" s="4"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="4"/>
+      <c r="N36" s="4"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -2124,8 +2409,13 @@
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -2135,8 +2425,13 @@
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
       <c r="I38" s="4"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
+      <c r="N38" s="4"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -2146,8 +2441,13 @@
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -2157,8 +2457,13 @@
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4"/>
+      <c r="N40" s="4"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -2168,8 +2473,13 @@
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J41" s="5"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -2179,8 +2489,13 @@
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="4"/>
+      <c r="N42" s="4"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -2190,8 +2505,13 @@
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J43" s="5"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -2201,8 +2521,13 @@
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4"/>
+      <c r="N44" s="4"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -2212,8 +2537,13 @@
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J45" s="5"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="5"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -2223,8 +2553,13 @@
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="4"/>
+      <c r="N46" s="4"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -2234,8 +2569,13 @@
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J47" s="5"/>
+      <c r="K47" s="5"/>
+      <c r="L47" s="5"/>
+      <c r="M47" s="5"/>
+      <c r="N47" s="5"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -2245,8 +2585,13 @@
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="4"/>
+      <c r="N48" s="4"/>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
@@ -2256,8 +2601,13 @@
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J49" s="5"/>
+      <c r="K49" s="5"/>
+      <c r="L49" s="5"/>
+      <c r="M49" s="5"/>
+      <c r="N49" s="5"/>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -2267,8 +2617,13 @@
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="4"/>
+      <c r="N50" s="4"/>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -2278,8 +2633,13 @@
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J51" s="5"/>
+      <c r="K51" s="5"/>
+      <c r="L51" s="5"/>
+      <c r="M51" s="5"/>
+      <c r="N51" s="5"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -2289,8 +2649,13 @@
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J52" s="4"/>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="4"/>
+      <c r="N52" s="4"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
@@ -2300,8 +2665,13 @@
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J53" s="5"/>
+      <c r="K53" s="5"/>
+      <c r="L53" s="5"/>
+      <c r="M53" s="5"/>
+      <c r="N53" s="5"/>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -2311,8 +2681,13 @@
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J54" s="4"/>
+      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="4"/>
+      <c r="N54" s="4"/>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -2322,8 +2697,13 @@
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J55" s="5"/>
+      <c r="K55" s="5"/>
+      <c r="L55" s="5"/>
+      <c r="M55" s="5"/>
+      <c r="N55" s="5"/>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -2333,8 +2713,13 @@
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="4"/>
+      <c r="N56" s="4"/>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -2344,8 +2729,13 @@
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J57" s="5"/>
+      <c r="K57" s="5"/>
+      <c r="L57" s="5"/>
+      <c r="M57" s="5"/>
+      <c r="N57" s="5"/>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -2355,8 +2745,13 @@
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
+      <c r="L58" s="4"/>
+      <c r="M58" s="4"/>
+      <c r="N58" s="4"/>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -2366,8 +2761,13 @@
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J59" s="5"/>
+      <c r="K59" s="5"/>
+      <c r="L59" s="5"/>
+      <c r="M59" s="5"/>
+      <c r="N59" s="5"/>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -2377,8 +2777,13 @@
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J60" s="4"/>
+      <c r="K60" s="4"/>
+      <c r="L60" s="4"/>
+      <c r="M60" s="4"/>
+      <c r="N60" s="4"/>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -2388,8 +2793,13 @@
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J61" s="5"/>
+      <c r="K61" s="5"/>
+      <c r="L61" s="5"/>
+      <c r="M61" s="5"/>
+      <c r="N61" s="5"/>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -2399,8 +2809,13 @@
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="4"/>
+      <c r="M62" s="4"/>
+      <c r="N62" s="4"/>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
@@ -2410,8 +2825,13 @@
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
       <c r="I63" s="5"/>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J63" s="5"/>
+      <c r="K63" s="5"/>
+      <c r="L63" s="5"/>
+      <c r="M63" s="5"/>
+      <c r="N63" s="5"/>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -2421,8 +2841,13 @@
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J64" s="4"/>
+      <c r="K64" s="4"/>
+      <c r="L64" s="4"/>
+      <c r="M64" s="4"/>
+      <c r="N64" s="4"/>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
@@ -2432,8 +2857,13 @@
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
       <c r="I65" s="5"/>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J65" s="5"/>
+      <c r="K65" s="5"/>
+      <c r="L65" s="5"/>
+      <c r="M65" s="5"/>
+      <c r="N65" s="5"/>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -2443,8 +2873,13 @@
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J66" s="4"/>
+      <c r="K66" s="4"/>
+      <c r="L66" s="4"/>
+      <c r="M66" s="4"/>
+      <c r="N66" s="4"/>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
@@ -2454,8 +2889,13 @@
       <c r="G67" s="5"/>
       <c r="H67" s="5"/>
       <c r="I67" s="5"/>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J67" s="5"/>
+      <c r="K67" s="5"/>
+      <c r="L67" s="5"/>
+      <c r="M67" s="5"/>
+      <c r="N67" s="5"/>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -2465,8 +2905,13 @@
       <c r="G68" s="4"/>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J68" s="4"/>
+      <c r="K68" s="4"/>
+      <c r="L68" s="4"/>
+      <c r="M68" s="4"/>
+      <c r="N68" s="4"/>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
@@ -2476,8 +2921,13 @@
       <c r="G69" s="5"/>
       <c r="H69" s="5"/>
       <c r="I69" s="5"/>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J69" s="5"/>
+      <c r="K69" s="5"/>
+      <c r="L69" s="5"/>
+      <c r="M69" s="5"/>
+      <c r="N69" s="5"/>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -2487,8 +2937,13 @@
       <c r="G70" s="4"/>
       <c r="H70" s="4"/>
       <c r="I70" s="4"/>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J70" s="4"/>
+      <c r="K70" s="4"/>
+      <c r="L70" s="4"/>
+      <c r="M70" s="4"/>
+      <c r="N70" s="4"/>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
@@ -2498,8 +2953,13 @@
       <c r="G71" s="5"/>
       <c r="H71" s="5"/>
       <c r="I71" s="5"/>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J71" s="5"/>
+      <c r="K71" s="5"/>
+      <c r="L71" s="5"/>
+      <c r="M71" s="5"/>
+      <c r="N71" s="5"/>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -2509,8 +2969,13 @@
       <c r="G72" s="4"/>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+      <c r="M72" s="4"/>
+      <c r="N72" s="4"/>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
@@ -2520,8 +2985,13 @@
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
       <c r="I73" s="5"/>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J73" s="5"/>
+      <c r="K73" s="5"/>
+      <c r="L73" s="5"/>
+      <c r="M73" s="5"/>
+      <c r="N73" s="5"/>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -2531,8 +3001,13 @@
       <c r="G74" s="4"/>
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="4"/>
+      <c r="N74" s="4"/>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
@@ -2542,8 +3017,13 @@
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
       <c r="I75" s="5"/>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J75" s="5"/>
+      <c r="K75" s="5"/>
+      <c r="L75" s="5"/>
+      <c r="M75" s="5"/>
+      <c r="N75" s="5"/>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -2553,8 +3033,13 @@
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J76" s="4"/>
+      <c r="K76" s="4"/>
+      <c r="L76" s="4"/>
+      <c r="M76" s="4"/>
+      <c r="N76" s="4"/>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
@@ -2564,8 +3049,13 @@
       <c r="G77" s="5"/>
       <c r="H77" s="5"/>
       <c r="I77" s="5"/>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J77" s="5"/>
+      <c r="K77" s="5"/>
+      <c r="L77" s="5"/>
+      <c r="M77" s="5"/>
+      <c r="N77" s="5"/>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -2575,8 +3065,13 @@
       <c r="G78" s="4"/>
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
+      <c r="L78" s="4"/>
+      <c r="M78" s="4"/>
+      <c r="N78" s="4"/>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
@@ -2586,8 +3081,13 @@
       <c r="G79" s="5"/>
       <c r="H79" s="5"/>
       <c r="I79" s="5"/>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J79" s="5"/>
+      <c r="K79" s="5"/>
+      <c r="L79" s="5"/>
+      <c r="M79" s="5"/>
+      <c r="N79" s="5"/>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -2597,8 +3097,13 @@
       <c r="G80" s="4"/>
       <c r="H80" s="4"/>
       <c r="I80" s="4"/>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J80" s="4"/>
+      <c r="K80" s="4"/>
+      <c r="L80" s="4"/>
+      <c r="M80" s="4"/>
+      <c r="N80" s="4"/>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="5"/>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
@@ -2608,8 +3113,13 @@
       <c r="G81" s="5"/>
       <c r="H81" s="5"/>
       <c r="I81" s="5"/>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J81" s="5"/>
+      <c r="K81" s="5"/>
+      <c r="L81" s="5"/>
+      <c r="M81" s="5"/>
+      <c r="N81" s="5"/>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
@@ -2619,8 +3129,13 @@
       <c r="G82" s="4"/>
       <c r="H82" s="4"/>
       <c r="I82" s="4"/>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J82" s="4"/>
+      <c r="K82" s="4"/>
+      <c r="L82" s="4"/>
+      <c r="M82" s="4"/>
+      <c r="N82" s="4"/>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="5"/>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
@@ -2630,8 +3145,13 @@
       <c r="G83" s="5"/>
       <c r="H83" s="5"/>
       <c r="I83" s="5"/>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J83" s="5"/>
+      <c r="K83" s="5"/>
+      <c r="L83" s="5"/>
+      <c r="M83" s="5"/>
+      <c r="N83" s="5"/>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -2641,8 +3161,13 @@
       <c r="G84" s="4"/>
       <c r="H84" s="4"/>
       <c r="I84" s="4"/>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J84" s="4"/>
+      <c r="K84" s="4"/>
+      <c r="L84" s="4"/>
+      <c r="M84" s="4"/>
+      <c r="N84" s="4"/>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="5"/>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
@@ -2652,8 +3177,13 @@
       <c r="G85" s="5"/>
       <c r="H85" s="5"/>
       <c r="I85" s="5"/>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J85" s="5"/>
+      <c r="K85" s="5"/>
+      <c r="L85" s="5"/>
+      <c r="M85" s="5"/>
+      <c r="N85" s="5"/>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
@@ -2663,8 +3193,13 @@
       <c r="G86" s="4"/>
       <c r="H86" s="4"/>
       <c r="I86" s="4"/>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J86" s="4"/>
+      <c r="K86" s="4"/>
+      <c r="L86" s="4"/>
+      <c r="M86" s="4"/>
+      <c r="N86" s="4"/>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="5"/>
       <c r="B87" s="5"/>
       <c r="C87" s="5"/>
@@ -2674,8 +3209,13 @@
       <c r="G87" s="5"/>
       <c r="H87" s="5"/>
       <c r="I87" s="5"/>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J87" s="5"/>
+      <c r="K87" s="5"/>
+      <c r="L87" s="5"/>
+      <c r="M87" s="5"/>
+      <c r="N87" s="5"/>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -2685,8 +3225,13 @@
       <c r="G88" s="4"/>
       <c r="H88" s="4"/>
       <c r="I88" s="4"/>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J88" s="4"/>
+      <c r="K88" s="4"/>
+      <c r="L88" s="4"/>
+      <c r="M88" s="4"/>
+      <c r="N88" s="4"/>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="5"/>
       <c r="B89" s="5"/>
       <c r="C89" s="5"/>
@@ -2696,8 +3241,13 @@
       <c r="G89" s="5"/>
       <c r="H89" s="5"/>
       <c r="I89" s="5"/>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J89" s="5"/>
+      <c r="K89" s="5"/>
+      <c r="L89" s="5"/>
+      <c r="M89" s="5"/>
+      <c r="N89" s="5"/>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -2707,8 +3257,13 @@
       <c r="G90" s="4"/>
       <c r="H90" s="4"/>
       <c r="I90" s="4"/>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J90" s="4"/>
+      <c r="K90" s="4"/>
+      <c r="L90" s="4"/>
+      <c r="M90" s="4"/>
+      <c r="N90" s="4"/>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="5"/>
       <c r="B91" s="5"/>
       <c r="C91" s="5"/>
@@ -2718,8 +3273,13 @@
       <c r="G91" s="5"/>
       <c r="H91" s="5"/>
       <c r="I91" s="5"/>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J91" s="5"/>
+      <c r="K91" s="5"/>
+      <c r="L91" s="5"/>
+      <c r="M91" s="5"/>
+      <c r="N91" s="5"/>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="4"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -2729,8 +3289,13 @@
       <c r="G92" s="4"/>
       <c r="H92" s="4"/>
       <c r="I92" s="4"/>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J92" s="4"/>
+      <c r="K92" s="4"/>
+      <c r="L92" s="4"/>
+      <c r="M92" s="4"/>
+      <c r="N92" s="4"/>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
       <c r="B93" s="5"/>
       <c r="C93" s="5"/>
@@ -2740,8 +3305,13 @@
       <c r="G93" s="5"/>
       <c r="H93" s="5"/>
       <c r="I93" s="5"/>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J93" s="5"/>
+      <c r="K93" s="5"/>
+      <c r="L93" s="5"/>
+      <c r="M93" s="5"/>
+      <c r="N93" s="5"/>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -2751,8 +3321,13 @@
       <c r="G94" s="4"/>
       <c r="H94" s="4"/>
       <c r="I94" s="4"/>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J94" s="4"/>
+      <c r="K94" s="4"/>
+      <c r="L94" s="4"/>
+      <c r="M94" s="4"/>
+      <c r="N94" s="4"/>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="5"/>
       <c r="B95" s="5"/>
       <c r="C95" s="5"/>
@@ -2762,8 +3337,13 @@
       <c r="G95" s="5"/>
       <c r="H95" s="5"/>
       <c r="I95" s="5"/>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J95" s="5"/>
+      <c r="K95" s="5"/>
+      <c r="L95" s="5"/>
+      <c r="M95" s="5"/>
+      <c r="N95" s="5"/>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -2773,8 +3353,13 @@
       <c r="G96" s="4"/>
       <c r="H96" s="4"/>
       <c r="I96" s="4"/>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J96" s="4"/>
+      <c r="K96" s="4"/>
+      <c r="L96" s="4"/>
+      <c r="M96" s="4"/>
+      <c r="N96" s="4"/>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="5"/>
       <c r="B97" s="5"/>
       <c r="C97" s="5"/>
@@ -2784,8 +3369,13 @@
       <c r="G97" s="5"/>
       <c r="H97" s="5"/>
       <c r="I97" s="5"/>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J97" s="5"/>
+      <c r="K97" s="5"/>
+      <c r="L97" s="5"/>
+      <c r="M97" s="5"/>
+      <c r="N97" s="5"/>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -2795,8 +3385,13 @@
       <c r="G98" s="4"/>
       <c r="H98" s="4"/>
       <c r="I98" s="4"/>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J98" s="4"/>
+      <c r="K98" s="4"/>
+      <c r="L98" s="4"/>
+      <c r="M98" s="4"/>
+      <c r="N98" s="4"/>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="5"/>
       <c r="B99" s="5"/>
       <c r="C99" s="5"/>
@@ -2806,8 +3401,13 @@
       <c r="G99" s="5"/>
       <c r="H99" s="5"/>
       <c r="I99" s="5"/>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J99" s="5"/>
+      <c r="K99" s="5"/>
+      <c r="L99" s="5"/>
+      <c r="M99" s="5"/>
+      <c r="N99" s="5"/>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -2817,8 +3417,13 @@
       <c r="G100" s="4"/>
       <c r="H100" s="4"/>
       <c r="I100" s="4"/>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J100" s="4"/>
+      <c r="K100" s="4"/>
+      <c r="L100" s="4"/>
+      <c r="M100" s="4"/>
+      <c r="N100" s="4"/>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="5"/>
       <c r="B101" s="5"/>
       <c r="C101" s="5"/>
@@ -2828,8 +3433,14 @@
       <c r="G101" s="5"/>
       <c r="H101" s="5"/>
       <c r="I101" s="5"/>
+      <c r="J101" s="5"/>
+      <c r="K101" s="5"/>
+      <c r="L101" s="5"/>
+      <c r="M101" s="5"/>
+      <c r="N101" s="5"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Size" prompt="Select a size" sqref="F2:F101" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"XS,S,M,L,XL,XXL,Free Size"</formula1>
@@ -2860,259 +3471,259 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A51"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>138</v>
       </c>
@@ -3124,8 +3735,8 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I102"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:N102"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="48" customWidth="1"/>
@@ -3138,8 +3749,8 @@
     <col min="9" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>139</v>
       </c>
       <c r="B1" s="7"/>
@@ -3151,7 +3762,7 @@
       <c r="H1" s="7"/>
       <c r="I1" s="7"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -3179,8 +3790,23 @@
       <c r="I2" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J2" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="str">
         <f>'Product Import'!A2</f>
         <v>Classic Cotton Tee</v>
@@ -3217,8 +3843,28 @@
         <f>'Product Import'!I2</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J3" s="5" t="str">
+        <f>IF('Product Import'!J2="", "", 'Product Import'!J2)</f>
+        <v>back.jpg</v>
+      </c>
+      <c r="K3" s="5" t="str">
+        <f>IF('Product Import'!K2="", "", 'Product Import'!K2)</f>
+        <v/>
+      </c>
+      <c r="L3" s="5" t="str">
+        <f>IF('Product Import'!L2="", "", 'Product Import'!L2)</f>
+        <v/>
+      </c>
+      <c r="M3" s="5" t="str">
+        <f>IF('Product Import'!M2="", "", 'Product Import'!M2)</f>
+        <v/>
+      </c>
+      <c r="N3" s="5" t="str">
+        <f>IF('Product Import'!N2="", "", 'Product Import'!N2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="str">
         <f>'Product Import'!A3</f>
         <v>Floral Croptop</v>
@@ -3255,8 +3901,28 @@
         <f>'Product Import'!I3</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J4" s="5" t="str">
+        <f>IF('Product Import'!J3="", "", 'Product Import'!J3)</f>
+        <v>back.jpg</v>
+      </c>
+      <c r="K4" s="5" t="str">
+        <f>IF('Product Import'!K3="", "", 'Product Import'!K3)</f>
+        <v/>
+      </c>
+      <c r="L4" s="5" t="str">
+        <f>IF('Product Import'!L3="", "", 'Product Import'!L3)</f>
+        <v/>
+      </c>
+      <c r="M4" s="5" t="str">
+        <f>IF('Product Import'!M3="", "", 'Product Import'!M3)</f>
+        <v/>
+      </c>
+      <c r="N4" s="5" t="str">
+        <f>IF('Product Import'!N3="", "", 'Product Import'!N3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="str">
         <f>'Product Import'!A4</f>
         <v>Kids Casual Dress</v>
@@ -3293,8 +3959,28 @@
         <f>'Product Import'!I4</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J5" s="5" t="str">
+        <f>IF('Product Import'!J4="", "", 'Product Import'!J4)</f>
+        <v>back.jpg</v>
+      </c>
+      <c r="K5" s="5" t="str">
+        <f>IF('Product Import'!K4="", "", 'Product Import'!K4)</f>
+        <v/>
+      </c>
+      <c r="L5" s="5" t="str">
+        <f>IF('Product Import'!L4="", "", 'Product Import'!L4)</f>
+        <v/>
+      </c>
+      <c r="M5" s="5" t="str">
+        <f>IF('Product Import'!M4="", "", 'Product Import'!M4)</f>
+        <v/>
+      </c>
+      <c r="N5" s="5" t="str">
+        <f>IF('Product Import'!N4="", "", 'Product Import'!N4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f>'Product Import'!A5</f>
         <v>0</v>
@@ -3331,8 +4017,28 @@
         <f>'Product Import'!I5</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J6" s="5" t="str">
+        <f>IF('Product Import'!J5="", "", 'Product Import'!J5)</f>
+        <v/>
+      </c>
+      <c r="K6" s="5" t="str">
+        <f>IF('Product Import'!K5="", "", 'Product Import'!K5)</f>
+        <v/>
+      </c>
+      <c r="L6" s="5" t="str">
+        <f>IF('Product Import'!L5="", "", 'Product Import'!L5)</f>
+        <v/>
+      </c>
+      <c r="M6" s="5" t="str">
+        <f>IF('Product Import'!M5="", "", 'Product Import'!M5)</f>
+        <v/>
+      </c>
+      <c r="N6" s="5" t="str">
+        <f>IF('Product Import'!N5="", "", 'Product Import'!N5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <f>'Product Import'!A6</f>
         <v>0</v>
@@ -3369,8 +4075,28 @@
         <f>'Product Import'!I6</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J7" s="5" t="str">
+        <f>IF('Product Import'!J6="", "", 'Product Import'!J6)</f>
+        <v/>
+      </c>
+      <c r="K7" s="5" t="str">
+        <f>IF('Product Import'!K6="", "", 'Product Import'!K6)</f>
+        <v/>
+      </c>
+      <c r="L7" s="5" t="str">
+        <f>IF('Product Import'!L6="", "", 'Product Import'!L6)</f>
+        <v/>
+      </c>
+      <c r="M7" s="5" t="str">
+        <f>IF('Product Import'!M6="", "", 'Product Import'!M6)</f>
+        <v/>
+      </c>
+      <c r="N7" s="5" t="str">
+        <f>IF('Product Import'!N6="", "", 'Product Import'!N6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f>'Product Import'!A7</f>
         <v>0</v>
@@ -3407,8 +4133,28 @@
         <f>'Product Import'!I7</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J8" s="5" t="str">
+        <f>IF('Product Import'!J7="", "", 'Product Import'!J7)</f>
+        <v/>
+      </c>
+      <c r="K8" s="5" t="str">
+        <f>IF('Product Import'!K7="", "", 'Product Import'!K7)</f>
+        <v/>
+      </c>
+      <c r="L8" s="5" t="str">
+        <f>IF('Product Import'!L7="", "", 'Product Import'!L7)</f>
+        <v/>
+      </c>
+      <c r="M8" s="5" t="str">
+        <f>IF('Product Import'!M7="", "", 'Product Import'!M7)</f>
+        <v/>
+      </c>
+      <c r="N8" s="5" t="str">
+        <f>IF('Product Import'!N7="", "", 'Product Import'!N7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <f>'Product Import'!A8</f>
         <v>0</v>
@@ -3445,8 +4191,28 @@
         <f>'Product Import'!I8</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J9" s="5" t="str">
+        <f>IF('Product Import'!J8="", "", 'Product Import'!J8)</f>
+        <v/>
+      </c>
+      <c r="K9" s="5" t="str">
+        <f>IF('Product Import'!K8="", "", 'Product Import'!K8)</f>
+        <v/>
+      </c>
+      <c r="L9" s="5" t="str">
+        <f>IF('Product Import'!L8="", "", 'Product Import'!L8)</f>
+        <v/>
+      </c>
+      <c r="M9" s="5" t="str">
+        <f>IF('Product Import'!M8="", "", 'Product Import'!M8)</f>
+        <v/>
+      </c>
+      <c r="N9" s="5" t="str">
+        <f>IF('Product Import'!N8="", "", 'Product Import'!N8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f>'Product Import'!A9</f>
         <v>0</v>
@@ -3483,8 +4249,28 @@
         <f>'Product Import'!I9</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J10" s="5" t="str">
+        <f>IF('Product Import'!J9="", "", 'Product Import'!J9)</f>
+        <v/>
+      </c>
+      <c r="K10" s="5" t="str">
+        <f>IF('Product Import'!K9="", "", 'Product Import'!K9)</f>
+        <v/>
+      </c>
+      <c r="L10" s="5" t="str">
+        <f>IF('Product Import'!L9="", "", 'Product Import'!L9)</f>
+        <v/>
+      </c>
+      <c r="M10" s="5" t="str">
+        <f>IF('Product Import'!M9="", "", 'Product Import'!M9)</f>
+        <v/>
+      </c>
+      <c r="N10" s="5" t="str">
+        <f>IF('Product Import'!N9="", "", 'Product Import'!N9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <f>'Product Import'!A10</f>
         <v>0</v>
@@ -3521,8 +4307,28 @@
         <f>'Product Import'!I10</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J11" s="5" t="str">
+        <f>IF('Product Import'!J10="", "", 'Product Import'!J10)</f>
+        <v/>
+      </c>
+      <c r="K11" s="5" t="str">
+        <f>IF('Product Import'!K10="", "", 'Product Import'!K10)</f>
+        <v/>
+      </c>
+      <c r="L11" s="5" t="str">
+        <f>IF('Product Import'!L10="", "", 'Product Import'!L10)</f>
+        <v/>
+      </c>
+      <c r="M11" s="5" t="str">
+        <f>IF('Product Import'!M10="", "", 'Product Import'!M10)</f>
+        <v/>
+      </c>
+      <c r="N11" s="5" t="str">
+        <f>IF('Product Import'!N10="", "", 'Product Import'!N10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <f>'Product Import'!A11</f>
         <v>0</v>
@@ -3559,8 +4365,28 @@
         <f>'Product Import'!I11</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J12" s="5" t="str">
+        <f>IF('Product Import'!J11="", "", 'Product Import'!J11)</f>
+        <v/>
+      </c>
+      <c r="K12" s="5" t="str">
+        <f>IF('Product Import'!K11="", "", 'Product Import'!K11)</f>
+        <v/>
+      </c>
+      <c r="L12" s="5" t="str">
+        <f>IF('Product Import'!L11="", "", 'Product Import'!L11)</f>
+        <v/>
+      </c>
+      <c r="M12" s="5" t="str">
+        <f>IF('Product Import'!M11="", "", 'Product Import'!M11)</f>
+        <v/>
+      </c>
+      <c r="N12" s="5" t="str">
+        <f>IF('Product Import'!N11="", "", 'Product Import'!N11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <f>'Product Import'!A12</f>
         <v>0</v>
@@ -3597,8 +4423,28 @@
         <f>'Product Import'!I12</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J13" s="5" t="str">
+        <f>IF('Product Import'!J12="", "", 'Product Import'!J12)</f>
+        <v/>
+      </c>
+      <c r="K13" s="5" t="str">
+        <f>IF('Product Import'!K12="", "", 'Product Import'!K12)</f>
+        <v/>
+      </c>
+      <c r="L13" s="5" t="str">
+        <f>IF('Product Import'!L12="", "", 'Product Import'!L12)</f>
+        <v/>
+      </c>
+      <c r="M13" s="5" t="str">
+        <f>IF('Product Import'!M12="", "", 'Product Import'!M12)</f>
+        <v/>
+      </c>
+      <c r="N13" s="5" t="str">
+        <f>IF('Product Import'!N12="", "", 'Product Import'!N12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <f>'Product Import'!A13</f>
         <v>0</v>
@@ -3635,8 +4481,28 @@
         <f>'Product Import'!I13</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J14" s="5" t="str">
+        <f>IF('Product Import'!J13="", "", 'Product Import'!J13)</f>
+        <v/>
+      </c>
+      <c r="K14" s="5" t="str">
+        <f>IF('Product Import'!K13="", "", 'Product Import'!K13)</f>
+        <v/>
+      </c>
+      <c r="L14" s="5" t="str">
+        <f>IF('Product Import'!L13="", "", 'Product Import'!L13)</f>
+        <v/>
+      </c>
+      <c r="M14" s="5" t="str">
+        <f>IF('Product Import'!M13="", "", 'Product Import'!M13)</f>
+        <v/>
+      </c>
+      <c r="N14" s="5" t="str">
+        <f>IF('Product Import'!N13="", "", 'Product Import'!N13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <f>'Product Import'!A14</f>
         <v>0</v>
@@ -3673,8 +4539,28 @@
         <f>'Product Import'!I14</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J15" s="5" t="str">
+        <f>IF('Product Import'!J14="", "", 'Product Import'!J14)</f>
+        <v/>
+      </c>
+      <c r="K15" s="5" t="str">
+        <f>IF('Product Import'!K14="", "", 'Product Import'!K14)</f>
+        <v/>
+      </c>
+      <c r="L15" s="5" t="str">
+        <f>IF('Product Import'!L14="", "", 'Product Import'!L14)</f>
+        <v/>
+      </c>
+      <c r="M15" s="5" t="str">
+        <f>IF('Product Import'!M14="", "", 'Product Import'!M14)</f>
+        <v/>
+      </c>
+      <c r="N15" s="5" t="str">
+        <f>IF('Product Import'!N14="", "", 'Product Import'!N14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <f>'Product Import'!A15</f>
         <v>0</v>
@@ -3711,8 +4597,28 @@
         <f>'Product Import'!I15</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J16" s="5" t="str">
+        <f>IF('Product Import'!J15="", "", 'Product Import'!J15)</f>
+        <v/>
+      </c>
+      <c r="K16" s="5" t="str">
+        <f>IF('Product Import'!K15="", "", 'Product Import'!K15)</f>
+        <v/>
+      </c>
+      <c r="L16" s="5" t="str">
+        <f>IF('Product Import'!L15="", "", 'Product Import'!L15)</f>
+        <v/>
+      </c>
+      <c r="M16" s="5" t="str">
+        <f>IF('Product Import'!M15="", "", 'Product Import'!M15)</f>
+        <v/>
+      </c>
+      <c r="N16" s="5" t="str">
+        <f>IF('Product Import'!N15="", "", 'Product Import'!N15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <f>'Product Import'!A16</f>
         <v>0</v>
@@ -3749,8 +4655,28 @@
         <f>'Product Import'!I16</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J17" s="5" t="str">
+        <f>IF('Product Import'!J16="", "", 'Product Import'!J16)</f>
+        <v/>
+      </c>
+      <c r="K17" s="5" t="str">
+        <f>IF('Product Import'!K16="", "", 'Product Import'!K16)</f>
+        <v/>
+      </c>
+      <c r="L17" s="5" t="str">
+        <f>IF('Product Import'!L16="", "", 'Product Import'!L16)</f>
+        <v/>
+      </c>
+      <c r="M17" s="5" t="str">
+        <f>IF('Product Import'!M16="", "", 'Product Import'!M16)</f>
+        <v/>
+      </c>
+      <c r="N17" s="5" t="str">
+        <f>IF('Product Import'!N16="", "", 'Product Import'!N16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <f>'Product Import'!A17</f>
         <v>0</v>
@@ -3787,8 +4713,28 @@
         <f>'Product Import'!I17</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J18" s="5" t="str">
+        <f>IF('Product Import'!J17="", "", 'Product Import'!J17)</f>
+        <v/>
+      </c>
+      <c r="K18" s="5" t="str">
+        <f>IF('Product Import'!K17="", "", 'Product Import'!K17)</f>
+        <v/>
+      </c>
+      <c r="L18" s="5" t="str">
+        <f>IF('Product Import'!L17="", "", 'Product Import'!L17)</f>
+        <v/>
+      </c>
+      <c r="M18" s="5" t="str">
+        <f>IF('Product Import'!M17="", "", 'Product Import'!M17)</f>
+        <v/>
+      </c>
+      <c r="N18" s="5" t="str">
+        <f>IF('Product Import'!N17="", "", 'Product Import'!N17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <f>'Product Import'!A18</f>
         <v>0</v>
@@ -3825,8 +4771,28 @@
         <f>'Product Import'!I18</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J19" s="5" t="str">
+        <f>IF('Product Import'!J18="", "", 'Product Import'!J18)</f>
+        <v/>
+      </c>
+      <c r="K19" s="5" t="str">
+        <f>IF('Product Import'!K18="", "", 'Product Import'!K18)</f>
+        <v/>
+      </c>
+      <c r="L19" s="5" t="str">
+        <f>IF('Product Import'!L18="", "", 'Product Import'!L18)</f>
+        <v/>
+      </c>
+      <c r="M19" s="5" t="str">
+        <f>IF('Product Import'!M18="", "", 'Product Import'!M18)</f>
+        <v/>
+      </c>
+      <c r="N19" s="5" t="str">
+        <f>IF('Product Import'!N18="", "", 'Product Import'!N18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <f>'Product Import'!A19</f>
         <v>0</v>
@@ -3863,8 +4829,28 @@
         <f>'Product Import'!I19</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J20" s="5" t="str">
+        <f>IF('Product Import'!J19="", "", 'Product Import'!J19)</f>
+        <v/>
+      </c>
+      <c r="K20" s="5" t="str">
+        <f>IF('Product Import'!K19="", "", 'Product Import'!K19)</f>
+        <v/>
+      </c>
+      <c r="L20" s="5" t="str">
+        <f>IF('Product Import'!L19="", "", 'Product Import'!L19)</f>
+        <v/>
+      </c>
+      <c r="M20" s="5" t="str">
+        <f>IF('Product Import'!M19="", "", 'Product Import'!M19)</f>
+        <v/>
+      </c>
+      <c r="N20" s="5" t="str">
+        <f>IF('Product Import'!N19="", "", 'Product Import'!N19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <f>'Product Import'!A20</f>
         <v>0</v>
@@ -3901,8 +4887,28 @@
         <f>'Product Import'!I20</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J21" s="5" t="str">
+        <f>IF('Product Import'!J20="", "", 'Product Import'!J20)</f>
+        <v/>
+      </c>
+      <c r="K21" s="5" t="str">
+        <f>IF('Product Import'!K20="", "", 'Product Import'!K20)</f>
+        <v/>
+      </c>
+      <c r="L21" s="5" t="str">
+        <f>IF('Product Import'!L20="", "", 'Product Import'!L20)</f>
+        <v/>
+      </c>
+      <c r="M21" s="5" t="str">
+        <f>IF('Product Import'!M20="", "", 'Product Import'!M20)</f>
+        <v/>
+      </c>
+      <c r="N21" s="5" t="str">
+        <f>IF('Product Import'!N20="", "", 'Product Import'!N20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <f>'Product Import'!A21</f>
         <v>0</v>
@@ -3939,8 +4945,28 @@
         <f>'Product Import'!I21</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J22" s="5" t="str">
+        <f>IF('Product Import'!J21="", "", 'Product Import'!J21)</f>
+        <v/>
+      </c>
+      <c r="K22" s="5" t="str">
+        <f>IF('Product Import'!K21="", "", 'Product Import'!K21)</f>
+        <v/>
+      </c>
+      <c r="L22" s="5" t="str">
+        <f>IF('Product Import'!L21="", "", 'Product Import'!L21)</f>
+        <v/>
+      </c>
+      <c r="M22" s="5" t="str">
+        <f>IF('Product Import'!M21="", "", 'Product Import'!M21)</f>
+        <v/>
+      </c>
+      <c r="N22" s="5" t="str">
+        <f>IF('Product Import'!N21="", "", 'Product Import'!N21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <f>'Product Import'!A22</f>
         <v>0</v>
@@ -3977,8 +5003,28 @@
         <f>'Product Import'!I22</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J23" s="5" t="str">
+        <f>IF('Product Import'!J22="", "", 'Product Import'!J22)</f>
+        <v/>
+      </c>
+      <c r="K23" s="5" t="str">
+        <f>IF('Product Import'!K22="", "", 'Product Import'!K22)</f>
+        <v/>
+      </c>
+      <c r="L23" s="5" t="str">
+        <f>IF('Product Import'!L22="", "", 'Product Import'!L22)</f>
+        <v/>
+      </c>
+      <c r="M23" s="5" t="str">
+        <f>IF('Product Import'!M22="", "", 'Product Import'!M22)</f>
+        <v/>
+      </c>
+      <c r="N23" s="5" t="str">
+        <f>IF('Product Import'!N22="", "", 'Product Import'!N22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <f>'Product Import'!A23</f>
         <v>0</v>
@@ -4015,8 +5061,28 @@
         <f>'Product Import'!I23</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J24" s="5" t="str">
+        <f>IF('Product Import'!J23="", "", 'Product Import'!J23)</f>
+        <v/>
+      </c>
+      <c r="K24" s="5" t="str">
+        <f>IF('Product Import'!K23="", "", 'Product Import'!K23)</f>
+        <v/>
+      </c>
+      <c r="L24" s="5" t="str">
+        <f>IF('Product Import'!L23="", "", 'Product Import'!L23)</f>
+        <v/>
+      </c>
+      <c r="M24" s="5" t="str">
+        <f>IF('Product Import'!M23="", "", 'Product Import'!M23)</f>
+        <v/>
+      </c>
+      <c r="N24" s="5" t="str">
+        <f>IF('Product Import'!N23="", "", 'Product Import'!N23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <f>'Product Import'!A24</f>
         <v>0</v>
@@ -4053,8 +5119,28 @@
         <f>'Product Import'!I24</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J25" s="5" t="str">
+        <f>IF('Product Import'!J24="", "", 'Product Import'!J24)</f>
+        <v/>
+      </c>
+      <c r="K25" s="5" t="str">
+        <f>IF('Product Import'!K24="", "", 'Product Import'!K24)</f>
+        <v/>
+      </c>
+      <c r="L25" s="5" t="str">
+        <f>IF('Product Import'!L24="", "", 'Product Import'!L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="5" t="str">
+        <f>IF('Product Import'!M24="", "", 'Product Import'!M24)</f>
+        <v/>
+      </c>
+      <c r="N25" s="5" t="str">
+        <f>IF('Product Import'!N24="", "", 'Product Import'!N24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <f>'Product Import'!A25</f>
         <v>0</v>
@@ -4091,8 +5177,28 @@
         <f>'Product Import'!I25</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J26" s="5" t="str">
+        <f>IF('Product Import'!J25="", "", 'Product Import'!J25)</f>
+        <v/>
+      </c>
+      <c r="K26" s="5" t="str">
+        <f>IF('Product Import'!K25="", "", 'Product Import'!K25)</f>
+        <v/>
+      </c>
+      <c r="L26" s="5" t="str">
+        <f>IF('Product Import'!L25="", "", 'Product Import'!L25)</f>
+        <v/>
+      </c>
+      <c r="M26" s="5" t="str">
+        <f>IF('Product Import'!M25="", "", 'Product Import'!M25)</f>
+        <v/>
+      </c>
+      <c r="N26" s="5" t="str">
+        <f>IF('Product Import'!N25="", "", 'Product Import'!N25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <f>'Product Import'!A26</f>
         <v>0</v>
@@ -4129,8 +5235,28 @@
         <f>'Product Import'!I26</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J27" s="5" t="str">
+        <f>IF('Product Import'!J26="", "", 'Product Import'!J26)</f>
+        <v/>
+      </c>
+      <c r="K27" s="5" t="str">
+        <f>IF('Product Import'!K26="", "", 'Product Import'!K26)</f>
+        <v/>
+      </c>
+      <c r="L27" s="5" t="str">
+        <f>IF('Product Import'!L26="", "", 'Product Import'!L26)</f>
+        <v/>
+      </c>
+      <c r="M27" s="5" t="str">
+        <f>IF('Product Import'!M26="", "", 'Product Import'!M26)</f>
+        <v/>
+      </c>
+      <c r="N27" s="5" t="str">
+        <f>IF('Product Import'!N26="", "", 'Product Import'!N26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <f>'Product Import'!A27</f>
         <v>0</v>
@@ -4167,8 +5293,28 @@
         <f>'Product Import'!I27</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J28" s="5" t="str">
+        <f>IF('Product Import'!J27="", "", 'Product Import'!J27)</f>
+        <v/>
+      </c>
+      <c r="K28" s="5" t="str">
+        <f>IF('Product Import'!K27="", "", 'Product Import'!K27)</f>
+        <v/>
+      </c>
+      <c r="L28" s="5" t="str">
+        <f>IF('Product Import'!L27="", "", 'Product Import'!L27)</f>
+        <v/>
+      </c>
+      <c r="M28" s="5" t="str">
+        <f>IF('Product Import'!M27="", "", 'Product Import'!M27)</f>
+        <v/>
+      </c>
+      <c r="N28" s="5" t="str">
+        <f>IF('Product Import'!N27="", "", 'Product Import'!N27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <f>'Product Import'!A28</f>
         <v>0</v>
@@ -4205,8 +5351,28 @@
         <f>'Product Import'!I28</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J29" s="5" t="str">
+        <f>IF('Product Import'!J28="", "", 'Product Import'!J28)</f>
+        <v/>
+      </c>
+      <c r="K29" s="5" t="str">
+        <f>IF('Product Import'!K28="", "", 'Product Import'!K28)</f>
+        <v/>
+      </c>
+      <c r="L29" s="5" t="str">
+        <f>IF('Product Import'!L28="", "", 'Product Import'!L28)</f>
+        <v/>
+      </c>
+      <c r="M29" s="5" t="str">
+        <f>IF('Product Import'!M28="", "", 'Product Import'!M28)</f>
+        <v/>
+      </c>
+      <c r="N29" s="5" t="str">
+        <f>IF('Product Import'!N28="", "", 'Product Import'!N28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <f>'Product Import'!A29</f>
         <v>0</v>
@@ -4243,8 +5409,28 @@
         <f>'Product Import'!I29</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J30" s="5" t="str">
+        <f>IF('Product Import'!J29="", "", 'Product Import'!J29)</f>
+        <v/>
+      </c>
+      <c r="K30" s="5" t="str">
+        <f>IF('Product Import'!K29="", "", 'Product Import'!K29)</f>
+        <v/>
+      </c>
+      <c r="L30" s="5" t="str">
+        <f>IF('Product Import'!L29="", "", 'Product Import'!L29)</f>
+        <v/>
+      </c>
+      <c r="M30" s="5" t="str">
+        <f>IF('Product Import'!M29="", "", 'Product Import'!M29)</f>
+        <v/>
+      </c>
+      <c r="N30" s="5" t="str">
+        <f>IF('Product Import'!N29="", "", 'Product Import'!N29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <f>'Product Import'!A30</f>
         <v>0</v>
@@ -4281,8 +5467,28 @@
         <f>'Product Import'!I30</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J31" s="5" t="str">
+        <f>IF('Product Import'!J30="", "", 'Product Import'!J30)</f>
+        <v/>
+      </c>
+      <c r="K31" s="5" t="str">
+        <f>IF('Product Import'!K30="", "", 'Product Import'!K30)</f>
+        <v/>
+      </c>
+      <c r="L31" s="5" t="str">
+        <f>IF('Product Import'!L30="", "", 'Product Import'!L30)</f>
+        <v/>
+      </c>
+      <c r="M31" s="5" t="str">
+        <f>IF('Product Import'!M30="", "", 'Product Import'!M30)</f>
+        <v/>
+      </c>
+      <c r="N31" s="5" t="str">
+        <f>IF('Product Import'!N30="", "", 'Product Import'!N30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <f>'Product Import'!A31</f>
         <v>0</v>
@@ -4319,8 +5525,28 @@
         <f>'Product Import'!I31</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J32" s="5" t="str">
+        <f>IF('Product Import'!J31="", "", 'Product Import'!J31)</f>
+        <v/>
+      </c>
+      <c r="K32" s="5" t="str">
+        <f>IF('Product Import'!K31="", "", 'Product Import'!K31)</f>
+        <v/>
+      </c>
+      <c r="L32" s="5" t="str">
+        <f>IF('Product Import'!L31="", "", 'Product Import'!L31)</f>
+        <v/>
+      </c>
+      <c r="M32" s="5" t="str">
+        <f>IF('Product Import'!M31="", "", 'Product Import'!M31)</f>
+        <v/>
+      </c>
+      <c r="N32" s="5" t="str">
+        <f>IF('Product Import'!N31="", "", 'Product Import'!N31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <f>'Product Import'!A32</f>
         <v>0</v>
@@ -4357,8 +5583,28 @@
         <f>'Product Import'!I32</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J33" s="5" t="str">
+        <f>IF('Product Import'!J32="", "", 'Product Import'!J32)</f>
+        <v/>
+      </c>
+      <c r="K33" s="5" t="str">
+        <f>IF('Product Import'!K32="", "", 'Product Import'!K32)</f>
+        <v/>
+      </c>
+      <c r="L33" s="5" t="str">
+        <f>IF('Product Import'!L32="", "", 'Product Import'!L32)</f>
+        <v/>
+      </c>
+      <c r="M33" s="5" t="str">
+        <f>IF('Product Import'!M32="", "", 'Product Import'!M32)</f>
+        <v/>
+      </c>
+      <c r="N33" s="5" t="str">
+        <f>IF('Product Import'!N32="", "", 'Product Import'!N32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <f>'Product Import'!A33</f>
         <v>0</v>
@@ -4395,8 +5641,28 @@
         <f>'Product Import'!I33</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J34" s="5" t="str">
+        <f>IF('Product Import'!J33="", "", 'Product Import'!J33)</f>
+        <v/>
+      </c>
+      <c r="K34" s="5" t="str">
+        <f>IF('Product Import'!K33="", "", 'Product Import'!K33)</f>
+        <v/>
+      </c>
+      <c r="L34" s="5" t="str">
+        <f>IF('Product Import'!L33="", "", 'Product Import'!L33)</f>
+        <v/>
+      </c>
+      <c r="M34" s="5" t="str">
+        <f>IF('Product Import'!M33="", "", 'Product Import'!M33)</f>
+        <v/>
+      </c>
+      <c r="N34" s="5" t="str">
+        <f>IF('Product Import'!N33="", "", 'Product Import'!N33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <f>'Product Import'!A34</f>
         <v>0</v>
@@ -4433,8 +5699,28 @@
         <f>'Product Import'!I34</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J35" s="5" t="str">
+        <f>IF('Product Import'!J34="", "", 'Product Import'!J34)</f>
+        <v/>
+      </c>
+      <c r="K35" s="5" t="str">
+        <f>IF('Product Import'!K34="", "", 'Product Import'!K34)</f>
+        <v/>
+      </c>
+      <c r="L35" s="5" t="str">
+        <f>IF('Product Import'!L34="", "", 'Product Import'!L34)</f>
+        <v/>
+      </c>
+      <c r="M35" s="5" t="str">
+        <f>IF('Product Import'!M34="", "", 'Product Import'!M34)</f>
+        <v/>
+      </c>
+      <c r="N35" s="5" t="str">
+        <f>IF('Product Import'!N34="", "", 'Product Import'!N34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <f>'Product Import'!A35</f>
         <v>0</v>
@@ -4471,8 +5757,28 @@
         <f>'Product Import'!I35</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J36" s="5" t="str">
+        <f>IF('Product Import'!J35="", "", 'Product Import'!J35)</f>
+        <v/>
+      </c>
+      <c r="K36" s="5" t="str">
+        <f>IF('Product Import'!K35="", "", 'Product Import'!K35)</f>
+        <v/>
+      </c>
+      <c r="L36" s="5" t="str">
+        <f>IF('Product Import'!L35="", "", 'Product Import'!L35)</f>
+        <v/>
+      </c>
+      <c r="M36" s="5" t="str">
+        <f>IF('Product Import'!M35="", "", 'Product Import'!M35)</f>
+        <v/>
+      </c>
+      <c r="N36" s="5" t="str">
+        <f>IF('Product Import'!N35="", "", 'Product Import'!N35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <f>'Product Import'!A36</f>
         <v>0</v>
@@ -4509,8 +5815,28 @@
         <f>'Product Import'!I36</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J37" s="5" t="str">
+        <f>IF('Product Import'!J36="", "", 'Product Import'!J36)</f>
+        <v/>
+      </c>
+      <c r="K37" s="5" t="str">
+        <f>IF('Product Import'!K36="", "", 'Product Import'!K36)</f>
+        <v/>
+      </c>
+      <c r="L37" s="5" t="str">
+        <f>IF('Product Import'!L36="", "", 'Product Import'!L36)</f>
+        <v/>
+      </c>
+      <c r="M37" s="5" t="str">
+        <f>IF('Product Import'!M36="", "", 'Product Import'!M36)</f>
+        <v/>
+      </c>
+      <c r="N37" s="5" t="str">
+        <f>IF('Product Import'!N36="", "", 'Product Import'!N36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <f>'Product Import'!A37</f>
         <v>0</v>
@@ -4547,8 +5873,28 @@
         <f>'Product Import'!I37</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J38" s="5" t="str">
+        <f>IF('Product Import'!J37="", "", 'Product Import'!J37)</f>
+        <v/>
+      </c>
+      <c r="K38" s="5" t="str">
+        <f>IF('Product Import'!K37="", "", 'Product Import'!K37)</f>
+        <v/>
+      </c>
+      <c r="L38" s="5" t="str">
+        <f>IF('Product Import'!L37="", "", 'Product Import'!L37)</f>
+        <v/>
+      </c>
+      <c r="M38" s="5" t="str">
+        <f>IF('Product Import'!M37="", "", 'Product Import'!M37)</f>
+        <v/>
+      </c>
+      <c r="N38" s="5" t="str">
+        <f>IF('Product Import'!N37="", "", 'Product Import'!N37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <f>'Product Import'!A38</f>
         <v>0</v>
@@ -4585,8 +5931,28 @@
         <f>'Product Import'!I38</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J39" s="5" t="str">
+        <f>IF('Product Import'!J38="", "", 'Product Import'!J38)</f>
+        <v/>
+      </c>
+      <c r="K39" s="5" t="str">
+        <f>IF('Product Import'!K38="", "", 'Product Import'!K38)</f>
+        <v/>
+      </c>
+      <c r="L39" s="5" t="str">
+        <f>IF('Product Import'!L38="", "", 'Product Import'!L38)</f>
+        <v/>
+      </c>
+      <c r="M39" s="5" t="str">
+        <f>IF('Product Import'!M38="", "", 'Product Import'!M38)</f>
+        <v/>
+      </c>
+      <c r="N39" s="5" t="str">
+        <f>IF('Product Import'!N38="", "", 'Product Import'!N38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <f>'Product Import'!A39</f>
         <v>0</v>
@@ -4623,8 +5989,28 @@
         <f>'Product Import'!I39</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J40" s="5" t="str">
+        <f>IF('Product Import'!J39="", "", 'Product Import'!J39)</f>
+        <v/>
+      </c>
+      <c r="K40" s="5" t="str">
+        <f>IF('Product Import'!K39="", "", 'Product Import'!K39)</f>
+        <v/>
+      </c>
+      <c r="L40" s="5" t="str">
+        <f>IF('Product Import'!L39="", "", 'Product Import'!L39)</f>
+        <v/>
+      </c>
+      <c r="M40" s="5" t="str">
+        <f>IF('Product Import'!M39="", "", 'Product Import'!M39)</f>
+        <v/>
+      </c>
+      <c r="N40" s="5" t="str">
+        <f>IF('Product Import'!N39="", "", 'Product Import'!N39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <f>'Product Import'!A40</f>
         <v>0</v>
@@ -4661,8 +6047,28 @@
         <f>'Product Import'!I40</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J41" s="5" t="str">
+        <f>IF('Product Import'!J40="", "", 'Product Import'!J40)</f>
+        <v/>
+      </c>
+      <c r="K41" s="5" t="str">
+        <f>IF('Product Import'!K40="", "", 'Product Import'!K40)</f>
+        <v/>
+      </c>
+      <c r="L41" s="5" t="str">
+        <f>IF('Product Import'!L40="", "", 'Product Import'!L40)</f>
+        <v/>
+      </c>
+      <c r="M41" s="5" t="str">
+        <f>IF('Product Import'!M40="", "", 'Product Import'!M40)</f>
+        <v/>
+      </c>
+      <c r="N41" s="5" t="str">
+        <f>IF('Product Import'!N40="", "", 'Product Import'!N40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <f>'Product Import'!A41</f>
         <v>0</v>
@@ -4699,8 +6105,28 @@
         <f>'Product Import'!I41</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J42" s="5" t="str">
+        <f>IF('Product Import'!J41="", "", 'Product Import'!J41)</f>
+        <v/>
+      </c>
+      <c r="K42" s="5" t="str">
+        <f>IF('Product Import'!K41="", "", 'Product Import'!K41)</f>
+        <v/>
+      </c>
+      <c r="L42" s="5" t="str">
+        <f>IF('Product Import'!L41="", "", 'Product Import'!L41)</f>
+        <v/>
+      </c>
+      <c r="M42" s="5" t="str">
+        <f>IF('Product Import'!M41="", "", 'Product Import'!M41)</f>
+        <v/>
+      </c>
+      <c r="N42" s="5" t="str">
+        <f>IF('Product Import'!N41="", "", 'Product Import'!N41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <f>'Product Import'!A42</f>
         <v>0</v>
@@ -4737,8 +6163,28 @@
         <f>'Product Import'!I42</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J43" s="5" t="str">
+        <f>IF('Product Import'!J42="", "", 'Product Import'!J42)</f>
+        <v/>
+      </c>
+      <c r="K43" s="5" t="str">
+        <f>IF('Product Import'!K42="", "", 'Product Import'!K42)</f>
+        <v/>
+      </c>
+      <c r="L43" s="5" t="str">
+        <f>IF('Product Import'!L42="", "", 'Product Import'!L42)</f>
+        <v/>
+      </c>
+      <c r="M43" s="5" t="str">
+        <f>IF('Product Import'!M42="", "", 'Product Import'!M42)</f>
+        <v/>
+      </c>
+      <c r="N43" s="5" t="str">
+        <f>IF('Product Import'!N42="", "", 'Product Import'!N42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <f>'Product Import'!A43</f>
         <v>0</v>
@@ -4775,8 +6221,28 @@
         <f>'Product Import'!I43</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J44" s="5" t="str">
+        <f>IF('Product Import'!J43="", "", 'Product Import'!J43)</f>
+        <v/>
+      </c>
+      <c r="K44" s="5" t="str">
+        <f>IF('Product Import'!K43="", "", 'Product Import'!K43)</f>
+        <v/>
+      </c>
+      <c r="L44" s="5" t="str">
+        <f>IF('Product Import'!L43="", "", 'Product Import'!L43)</f>
+        <v/>
+      </c>
+      <c r="M44" s="5" t="str">
+        <f>IF('Product Import'!M43="", "", 'Product Import'!M43)</f>
+        <v/>
+      </c>
+      <c r="N44" s="5" t="str">
+        <f>IF('Product Import'!N43="", "", 'Product Import'!N43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <f>'Product Import'!A44</f>
         <v>0</v>
@@ -4813,8 +6279,28 @@
         <f>'Product Import'!I44</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J45" s="5" t="str">
+        <f>IF('Product Import'!J44="", "", 'Product Import'!J44)</f>
+        <v/>
+      </c>
+      <c r="K45" s="5" t="str">
+        <f>IF('Product Import'!K44="", "", 'Product Import'!K44)</f>
+        <v/>
+      </c>
+      <c r="L45" s="5" t="str">
+        <f>IF('Product Import'!L44="", "", 'Product Import'!L44)</f>
+        <v/>
+      </c>
+      <c r="M45" s="5" t="str">
+        <f>IF('Product Import'!M44="", "", 'Product Import'!M44)</f>
+        <v/>
+      </c>
+      <c r="N45" s="5" t="str">
+        <f>IF('Product Import'!N44="", "", 'Product Import'!N44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <f>'Product Import'!A45</f>
         <v>0</v>
@@ -4851,8 +6337,28 @@
         <f>'Product Import'!I45</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J46" s="5" t="str">
+        <f>IF('Product Import'!J45="", "", 'Product Import'!J45)</f>
+        <v/>
+      </c>
+      <c r="K46" s="5" t="str">
+        <f>IF('Product Import'!K45="", "", 'Product Import'!K45)</f>
+        <v/>
+      </c>
+      <c r="L46" s="5" t="str">
+        <f>IF('Product Import'!L45="", "", 'Product Import'!L45)</f>
+        <v/>
+      </c>
+      <c r="M46" s="5" t="str">
+        <f>IF('Product Import'!M45="", "", 'Product Import'!M45)</f>
+        <v/>
+      </c>
+      <c r="N46" s="5" t="str">
+        <f>IF('Product Import'!N45="", "", 'Product Import'!N45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <f>'Product Import'!A46</f>
         <v>0</v>
@@ -4889,8 +6395,28 @@
         <f>'Product Import'!I46</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J47" s="5" t="str">
+        <f>IF('Product Import'!J46="", "", 'Product Import'!J46)</f>
+        <v/>
+      </c>
+      <c r="K47" s="5" t="str">
+        <f>IF('Product Import'!K46="", "", 'Product Import'!K46)</f>
+        <v/>
+      </c>
+      <c r="L47" s="5" t="str">
+        <f>IF('Product Import'!L46="", "", 'Product Import'!L46)</f>
+        <v/>
+      </c>
+      <c r="M47" s="5" t="str">
+        <f>IF('Product Import'!M46="", "", 'Product Import'!M46)</f>
+        <v/>
+      </c>
+      <c r="N47" s="5" t="str">
+        <f>IF('Product Import'!N46="", "", 'Product Import'!N46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <f>'Product Import'!A47</f>
         <v>0</v>
@@ -4927,8 +6453,28 @@
         <f>'Product Import'!I47</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J48" s="5" t="str">
+        <f>IF('Product Import'!J47="", "", 'Product Import'!J47)</f>
+        <v/>
+      </c>
+      <c r="K48" s="5" t="str">
+        <f>IF('Product Import'!K47="", "", 'Product Import'!K47)</f>
+        <v/>
+      </c>
+      <c r="L48" s="5" t="str">
+        <f>IF('Product Import'!L47="", "", 'Product Import'!L47)</f>
+        <v/>
+      </c>
+      <c r="M48" s="5" t="str">
+        <f>IF('Product Import'!M47="", "", 'Product Import'!M47)</f>
+        <v/>
+      </c>
+      <c r="N48" s="5" t="str">
+        <f>IF('Product Import'!N47="", "", 'Product Import'!N47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <f>'Product Import'!A48</f>
         <v>0</v>
@@ -4965,8 +6511,28 @@
         <f>'Product Import'!I48</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J49" s="5" t="str">
+        <f>IF('Product Import'!J48="", "", 'Product Import'!J48)</f>
+        <v/>
+      </c>
+      <c r="K49" s="5" t="str">
+        <f>IF('Product Import'!K48="", "", 'Product Import'!K48)</f>
+        <v/>
+      </c>
+      <c r="L49" s="5" t="str">
+        <f>IF('Product Import'!L48="", "", 'Product Import'!L48)</f>
+        <v/>
+      </c>
+      <c r="M49" s="5" t="str">
+        <f>IF('Product Import'!M48="", "", 'Product Import'!M48)</f>
+        <v/>
+      </c>
+      <c r="N49" s="5" t="str">
+        <f>IF('Product Import'!N48="", "", 'Product Import'!N48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <f>'Product Import'!A49</f>
         <v>0</v>
@@ -5003,8 +6569,28 @@
         <f>'Product Import'!I49</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J50" s="5" t="str">
+        <f>IF('Product Import'!J49="", "", 'Product Import'!J49)</f>
+        <v/>
+      </c>
+      <c r="K50" s="5" t="str">
+        <f>IF('Product Import'!K49="", "", 'Product Import'!K49)</f>
+        <v/>
+      </c>
+      <c r="L50" s="5" t="str">
+        <f>IF('Product Import'!L49="", "", 'Product Import'!L49)</f>
+        <v/>
+      </c>
+      <c r="M50" s="5" t="str">
+        <f>IF('Product Import'!M49="", "", 'Product Import'!M49)</f>
+        <v/>
+      </c>
+      <c r="N50" s="5" t="str">
+        <f>IF('Product Import'!N49="", "", 'Product Import'!N49)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <f>'Product Import'!A50</f>
         <v>0</v>
@@ -5041,8 +6627,28 @@
         <f>'Product Import'!I50</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J51" s="5" t="str">
+        <f>IF('Product Import'!J50="", "", 'Product Import'!J50)</f>
+        <v/>
+      </c>
+      <c r="K51" s="5" t="str">
+        <f>IF('Product Import'!K50="", "", 'Product Import'!K50)</f>
+        <v/>
+      </c>
+      <c r="L51" s="5" t="str">
+        <f>IF('Product Import'!L50="", "", 'Product Import'!L50)</f>
+        <v/>
+      </c>
+      <c r="M51" s="5" t="str">
+        <f>IF('Product Import'!M50="", "", 'Product Import'!M50)</f>
+        <v/>
+      </c>
+      <c r="N51" s="5" t="str">
+        <f>IF('Product Import'!N50="", "", 'Product Import'!N50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <f>'Product Import'!A51</f>
         <v>0</v>
@@ -5079,8 +6685,28 @@
         <f>'Product Import'!I51</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J52" s="5" t="str">
+        <f>IF('Product Import'!J51="", "", 'Product Import'!J51)</f>
+        <v/>
+      </c>
+      <c r="K52" s="5" t="str">
+        <f>IF('Product Import'!K51="", "", 'Product Import'!K51)</f>
+        <v/>
+      </c>
+      <c r="L52" s="5" t="str">
+        <f>IF('Product Import'!L51="", "", 'Product Import'!L51)</f>
+        <v/>
+      </c>
+      <c r="M52" s="5" t="str">
+        <f>IF('Product Import'!M51="", "", 'Product Import'!M51)</f>
+        <v/>
+      </c>
+      <c r="N52" s="5" t="str">
+        <f>IF('Product Import'!N51="", "", 'Product Import'!N51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
         <f>'Product Import'!A52</f>
         <v>0</v>
@@ -5117,8 +6743,28 @@
         <f>'Product Import'!I52</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J53" s="5" t="str">
+        <f>IF('Product Import'!J52="", "", 'Product Import'!J52)</f>
+        <v/>
+      </c>
+      <c r="K53" s="5" t="str">
+        <f>IF('Product Import'!K52="", "", 'Product Import'!K52)</f>
+        <v/>
+      </c>
+      <c r="L53" s="5" t="str">
+        <f>IF('Product Import'!L52="", "", 'Product Import'!L52)</f>
+        <v/>
+      </c>
+      <c r="M53" s="5" t="str">
+        <f>IF('Product Import'!M52="", "", 'Product Import'!M52)</f>
+        <v/>
+      </c>
+      <c r="N53" s="5" t="str">
+        <f>IF('Product Import'!N52="", "", 'Product Import'!N52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <f>'Product Import'!A53</f>
         <v>0</v>
@@ -5155,8 +6801,28 @@
         <f>'Product Import'!I53</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J54" s="5" t="str">
+        <f>IF('Product Import'!J53="", "", 'Product Import'!J53)</f>
+        <v/>
+      </c>
+      <c r="K54" s="5" t="str">
+        <f>IF('Product Import'!K53="", "", 'Product Import'!K53)</f>
+        <v/>
+      </c>
+      <c r="L54" s="5" t="str">
+        <f>IF('Product Import'!L53="", "", 'Product Import'!L53)</f>
+        <v/>
+      </c>
+      <c r="M54" s="5" t="str">
+        <f>IF('Product Import'!M53="", "", 'Product Import'!M53)</f>
+        <v/>
+      </c>
+      <c r="N54" s="5" t="str">
+        <f>IF('Product Import'!N53="", "", 'Product Import'!N53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <f>'Product Import'!A54</f>
         <v>0</v>
@@ -5193,8 +6859,28 @@
         <f>'Product Import'!I54</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J55" s="5" t="str">
+        <f>IF('Product Import'!J54="", "", 'Product Import'!J54)</f>
+        <v/>
+      </c>
+      <c r="K55" s="5" t="str">
+        <f>IF('Product Import'!K54="", "", 'Product Import'!K54)</f>
+        <v/>
+      </c>
+      <c r="L55" s="5" t="str">
+        <f>IF('Product Import'!L54="", "", 'Product Import'!L54)</f>
+        <v/>
+      </c>
+      <c r="M55" s="5" t="str">
+        <f>IF('Product Import'!M54="", "", 'Product Import'!M54)</f>
+        <v/>
+      </c>
+      <c r="N55" s="5" t="str">
+        <f>IF('Product Import'!N54="", "", 'Product Import'!N54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
         <f>'Product Import'!A55</f>
         <v>0</v>
@@ -5231,8 +6917,28 @@
         <f>'Product Import'!I55</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J56" s="5" t="str">
+        <f>IF('Product Import'!J55="", "", 'Product Import'!J55)</f>
+        <v/>
+      </c>
+      <c r="K56" s="5" t="str">
+        <f>IF('Product Import'!K55="", "", 'Product Import'!K55)</f>
+        <v/>
+      </c>
+      <c r="L56" s="5" t="str">
+        <f>IF('Product Import'!L55="", "", 'Product Import'!L55)</f>
+        <v/>
+      </c>
+      <c r="M56" s="5" t="str">
+        <f>IF('Product Import'!M55="", "", 'Product Import'!M55)</f>
+        <v/>
+      </c>
+      <c r="N56" s="5" t="str">
+        <f>IF('Product Import'!N55="", "", 'Product Import'!N55)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
         <f>'Product Import'!A56</f>
         <v>0</v>
@@ -5269,8 +6975,28 @@
         <f>'Product Import'!I56</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J57" s="5" t="str">
+        <f>IF('Product Import'!J56="", "", 'Product Import'!J56)</f>
+        <v/>
+      </c>
+      <c r="K57" s="5" t="str">
+        <f>IF('Product Import'!K56="", "", 'Product Import'!K56)</f>
+        <v/>
+      </c>
+      <c r="L57" s="5" t="str">
+        <f>IF('Product Import'!L56="", "", 'Product Import'!L56)</f>
+        <v/>
+      </c>
+      <c r="M57" s="5" t="str">
+        <f>IF('Product Import'!M56="", "", 'Product Import'!M56)</f>
+        <v/>
+      </c>
+      <c r="N57" s="5" t="str">
+        <f>IF('Product Import'!N56="", "", 'Product Import'!N56)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
         <f>'Product Import'!A57</f>
         <v>0</v>
@@ -5307,8 +7033,28 @@
         <f>'Product Import'!I57</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J58" s="5" t="str">
+        <f>IF('Product Import'!J57="", "", 'Product Import'!J57)</f>
+        <v/>
+      </c>
+      <c r="K58" s="5" t="str">
+        <f>IF('Product Import'!K57="", "", 'Product Import'!K57)</f>
+        <v/>
+      </c>
+      <c r="L58" s="5" t="str">
+        <f>IF('Product Import'!L57="", "", 'Product Import'!L57)</f>
+        <v/>
+      </c>
+      <c r="M58" s="5" t="str">
+        <f>IF('Product Import'!M57="", "", 'Product Import'!M57)</f>
+        <v/>
+      </c>
+      <c r="N58" s="5" t="str">
+        <f>IF('Product Import'!N57="", "", 'Product Import'!N57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
         <f>'Product Import'!A58</f>
         <v>0</v>
@@ -5345,8 +7091,28 @@
         <f>'Product Import'!I58</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J59" s="5" t="str">
+        <f>IF('Product Import'!J58="", "", 'Product Import'!J58)</f>
+        <v/>
+      </c>
+      <c r="K59" s="5" t="str">
+        <f>IF('Product Import'!K58="", "", 'Product Import'!K58)</f>
+        <v/>
+      </c>
+      <c r="L59" s="5" t="str">
+        <f>IF('Product Import'!L58="", "", 'Product Import'!L58)</f>
+        <v/>
+      </c>
+      <c r="M59" s="5" t="str">
+        <f>IF('Product Import'!M58="", "", 'Product Import'!M58)</f>
+        <v/>
+      </c>
+      <c r="N59" s="5" t="str">
+        <f>IF('Product Import'!N58="", "", 'Product Import'!N58)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <f>'Product Import'!A59</f>
         <v>0</v>
@@ -5383,8 +7149,28 @@
         <f>'Product Import'!I59</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J60" s="5" t="str">
+        <f>IF('Product Import'!J59="", "", 'Product Import'!J59)</f>
+        <v/>
+      </c>
+      <c r="K60" s="5" t="str">
+        <f>IF('Product Import'!K59="", "", 'Product Import'!K59)</f>
+        <v/>
+      </c>
+      <c r="L60" s="5" t="str">
+        <f>IF('Product Import'!L59="", "", 'Product Import'!L59)</f>
+        <v/>
+      </c>
+      <c r="M60" s="5" t="str">
+        <f>IF('Product Import'!M59="", "", 'Product Import'!M59)</f>
+        <v/>
+      </c>
+      <c r="N60" s="5" t="str">
+        <f>IF('Product Import'!N59="", "", 'Product Import'!N59)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <f>'Product Import'!A60</f>
         <v>0</v>
@@ -5421,8 +7207,28 @@
         <f>'Product Import'!I60</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J61" s="5" t="str">
+        <f>IF('Product Import'!J60="", "", 'Product Import'!J60)</f>
+        <v/>
+      </c>
+      <c r="K61" s="5" t="str">
+        <f>IF('Product Import'!K60="", "", 'Product Import'!K60)</f>
+        <v/>
+      </c>
+      <c r="L61" s="5" t="str">
+        <f>IF('Product Import'!L60="", "", 'Product Import'!L60)</f>
+        <v/>
+      </c>
+      <c r="M61" s="5" t="str">
+        <f>IF('Product Import'!M60="", "", 'Product Import'!M60)</f>
+        <v/>
+      </c>
+      <c r="N61" s="5" t="str">
+        <f>IF('Product Import'!N60="", "", 'Product Import'!N60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <f>'Product Import'!A61</f>
         <v>0</v>
@@ -5459,8 +7265,28 @@
         <f>'Product Import'!I61</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J62" s="5" t="str">
+        <f>IF('Product Import'!J61="", "", 'Product Import'!J61)</f>
+        <v/>
+      </c>
+      <c r="K62" s="5" t="str">
+        <f>IF('Product Import'!K61="", "", 'Product Import'!K61)</f>
+        <v/>
+      </c>
+      <c r="L62" s="5" t="str">
+        <f>IF('Product Import'!L61="", "", 'Product Import'!L61)</f>
+        <v/>
+      </c>
+      <c r="M62" s="5" t="str">
+        <f>IF('Product Import'!M61="", "", 'Product Import'!M61)</f>
+        <v/>
+      </c>
+      <c r="N62" s="5" t="str">
+        <f>IF('Product Import'!N61="", "", 'Product Import'!N61)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
         <f>'Product Import'!A62</f>
         <v>0</v>
@@ -5497,8 +7323,28 @@
         <f>'Product Import'!I62</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J63" s="5" t="str">
+        <f>IF('Product Import'!J62="", "", 'Product Import'!J62)</f>
+        <v/>
+      </c>
+      <c r="K63" s="5" t="str">
+        <f>IF('Product Import'!K62="", "", 'Product Import'!K62)</f>
+        <v/>
+      </c>
+      <c r="L63" s="5" t="str">
+        <f>IF('Product Import'!L62="", "", 'Product Import'!L62)</f>
+        <v/>
+      </c>
+      <c r="M63" s="5" t="str">
+        <f>IF('Product Import'!M62="", "", 'Product Import'!M62)</f>
+        <v/>
+      </c>
+      <c r="N63" s="5" t="str">
+        <f>IF('Product Import'!N62="", "", 'Product Import'!N62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <f>'Product Import'!A63</f>
         <v>0</v>
@@ -5535,8 +7381,28 @@
         <f>'Product Import'!I63</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J64" s="5" t="str">
+        <f>IF('Product Import'!J63="", "", 'Product Import'!J63)</f>
+        <v/>
+      </c>
+      <c r="K64" s="5" t="str">
+        <f>IF('Product Import'!K63="", "", 'Product Import'!K63)</f>
+        <v/>
+      </c>
+      <c r="L64" s="5" t="str">
+        <f>IF('Product Import'!L63="", "", 'Product Import'!L63)</f>
+        <v/>
+      </c>
+      <c r="M64" s="5" t="str">
+        <f>IF('Product Import'!M63="", "", 'Product Import'!M63)</f>
+        <v/>
+      </c>
+      <c r="N64" s="5" t="str">
+        <f>IF('Product Import'!N63="", "", 'Product Import'!N63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
         <f>'Product Import'!A64</f>
         <v>0</v>
@@ -5573,8 +7439,28 @@
         <f>'Product Import'!I64</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J65" s="5" t="str">
+        <f>IF('Product Import'!J64="", "", 'Product Import'!J64)</f>
+        <v/>
+      </c>
+      <c r="K65" s="5" t="str">
+        <f>IF('Product Import'!K64="", "", 'Product Import'!K64)</f>
+        <v/>
+      </c>
+      <c r="L65" s="5" t="str">
+        <f>IF('Product Import'!L64="", "", 'Product Import'!L64)</f>
+        <v/>
+      </c>
+      <c r="M65" s="5" t="str">
+        <f>IF('Product Import'!M64="", "", 'Product Import'!M64)</f>
+        <v/>
+      </c>
+      <c r="N65" s="5" t="str">
+        <f>IF('Product Import'!N64="", "", 'Product Import'!N64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
         <f>'Product Import'!A65</f>
         <v>0</v>
@@ -5611,8 +7497,28 @@
         <f>'Product Import'!I65</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J66" s="5" t="str">
+        <f>IF('Product Import'!J65="", "", 'Product Import'!J65)</f>
+        <v/>
+      </c>
+      <c r="K66" s="5" t="str">
+        <f>IF('Product Import'!K65="", "", 'Product Import'!K65)</f>
+        <v/>
+      </c>
+      <c r="L66" s="5" t="str">
+        <f>IF('Product Import'!L65="", "", 'Product Import'!L65)</f>
+        <v/>
+      </c>
+      <c r="M66" s="5" t="str">
+        <f>IF('Product Import'!M65="", "", 'Product Import'!M65)</f>
+        <v/>
+      </c>
+      <c r="N66" s="5" t="str">
+        <f>IF('Product Import'!N65="", "", 'Product Import'!N65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
         <f>'Product Import'!A66</f>
         <v>0</v>
@@ -5649,8 +7555,28 @@
         <f>'Product Import'!I66</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J67" s="5" t="str">
+        <f>IF('Product Import'!J66="", "", 'Product Import'!J66)</f>
+        <v/>
+      </c>
+      <c r="K67" s="5" t="str">
+        <f>IF('Product Import'!K66="", "", 'Product Import'!K66)</f>
+        <v/>
+      </c>
+      <c r="L67" s="5" t="str">
+        <f>IF('Product Import'!L66="", "", 'Product Import'!L66)</f>
+        <v/>
+      </c>
+      <c r="M67" s="5" t="str">
+        <f>IF('Product Import'!M66="", "", 'Product Import'!M66)</f>
+        <v/>
+      </c>
+      <c r="N67" s="5" t="str">
+        <f>IF('Product Import'!N66="", "", 'Product Import'!N66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
         <f>'Product Import'!A67</f>
         <v>0</v>
@@ -5687,8 +7613,28 @@
         <f>'Product Import'!I67</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J68" s="5" t="str">
+        <f>IF('Product Import'!J67="", "", 'Product Import'!J67)</f>
+        <v/>
+      </c>
+      <c r="K68" s="5" t="str">
+        <f>IF('Product Import'!K67="", "", 'Product Import'!K67)</f>
+        <v/>
+      </c>
+      <c r="L68" s="5" t="str">
+        <f>IF('Product Import'!L67="", "", 'Product Import'!L67)</f>
+        <v/>
+      </c>
+      <c r="M68" s="5" t="str">
+        <f>IF('Product Import'!M67="", "", 'Product Import'!M67)</f>
+        <v/>
+      </c>
+      <c r="N68" s="5" t="str">
+        <f>IF('Product Import'!N67="", "", 'Product Import'!N67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
         <f>'Product Import'!A68</f>
         <v>0</v>
@@ -5725,8 +7671,28 @@
         <f>'Product Import'!I68</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J69" s="5" t="str">
+        <f>IF('Product Import'!J68="", "", 'Product Import'!J68)</f>
+        <v/>
+      </c>
+      <c r="K69" s="5" t="str">
+        <f>IF('Product Import'!K68="", "", 'Product Import'!K68)</f>
+        <v/>
+      </c>
+      <c r="L69" s="5" t="str">
+        <f>IF('Product Import'!L68="", "", 'Product Import'!L68)</f>
+        <v/>
+      </c>
+      <c r="M69" s="5" t="str">
+        <f>IF('Product Import'!M68="", "", 'Product Import'!M68)</f>
+        <v/>
+      </c>
+      <c r="N69" s="5" t="str">
+        <f>IF('Product Import'!N68="", "", 'Product Import'!N68)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <f>'Product Import'!A69</f>
         <v>0</v>
@@ -5763,8 +7729,28 @@
         <f>'Product Import'!I69</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J70" s="5" t="str">
+        <f>IF('Product Import'!J69="", "", 'Product Import'!J69)</f>
+        <v/>
+      </c>
+      <c r="K70" s="5" t="str">
+        <f>IF('Product Import'!K69="", "", 'Product Import'!K69)</f>
+        <v/>
+      </c>
+      <c r="L70" s="5" t="str">
+        <f>IF('Product Import'!L69="", "", 'Product Import'!L69)</f>
+        <v/>
+      </c>
+      <c r="M70" s="5" t="str">
+        <f>IF('Product Import'!M69="", "", 'Product Import'!M69)</f>
+        <v/>
+      </c>
+      <c r="N70" s="5" t="str">
+        <f>IF('Product Import'!N69="", "", 'Product Import'!N69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
         <f>'Product Import'!A70</f>
         <v>0</v>
@@ -5801,8 +7787,28 @@
         <f>'Product Import'!I70</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J71" s="5" t="str">
+        <f>IF('Product Import'!J70="", "", 'Product Import'!J70)</f>
+        <v/>
+      </c>
+      <c r="K71" s="5" t="str">
+        <f>IF('Product Import'!K70="", "", 'Product Import'!K70)</f>
+        <v/>
+      </c>
+      <c r="L71" s="5" t="str">
+        <f>IF('Product Import'!L70="", "", 'Product Import'!L70)</f>
+        <v/>
+      </c>
+      <c r="M71" s="5" t="str">
+        <f>IF('Product Import'!M70="", "", 'Product Import'!M70)</f>
+        <v/>
+      </c>
+      <c r="N71" s="5" t="str">
+        <f>IF('Product Import'!N70="", "", 'Product Import'!N70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
         <f>'Product Import'!A71</f>
         <v>0</v>
@@ -5839,8 +7845,28 @@
         <f>'Product Import'!I71</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J72" s="5" t="str">
+        <f>IF('Product Import'!J71="", "", 'Product Import'!J71)</f>
+        <v/>
+      </c>
+      <c r="K72" s="5" t="str">
+        <f>IF('Product Import'!K71="", "", 'Product Import'!K71)</f>
+        <v/>
+      </c>
+      <c r="L72" s="5" t="str">
+        <f>IF('Product Import'!L71="", "", 'Product Import'!L71)</f>
+        <v/>
+      </c>
+      <c r="M72" s="5" t="str">
+        <f>IF('Product Import'!M71="", "", 'Product Import'!M71)</f>
+        <v/>
+      </c>
+      <c r="N72" s="5" t="str">
+        <f>IF('Product Import'!N71="", "", 'Product Import'!N71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
         <f>'Product Import'!A72</f>
         <v>0</v>
@@ -5877,8 +7903,28 @@
         <f>'Product Import'!I72</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J73" s="5" t="str">
+        <f>IF('Product Import'!J72="", "", 'Product Import'!J72)</f>
+        <v/>
+      </c>
+      <c r="K73" s="5" t="str">
+        <f>IF('Product Import'!K72="", "", 'Product Import'!K72)</f>
+        <v/>
+      </c>
+      <c r="L73" s="5" t="str">
+        <f>IF('Product Import'!L72="", "", 'Product Import'!L72)</f>
+        <v/>
+      </c>
+      <c r="M73" s="5" t="str">
+        <f>IF('Product Import'!M72="", "", 'Product Import'!M72)</f>
+        <v/>
+      </c>
+      <c r="N73" s="5" t="str">
+        <f>IF('Product Import'!N72="", "", 'Product Import'!N72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
         <f>'Product Import'!A73</f>
         <v>0</v>
@@ -5915,8 +7961,28 @@
         <f>'Product Import'!I73</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J74" s="5" t="str">
+        <f>IF('Product Import'!J73="", "", 'Product Import'!J73)</f>
+        <v/>
+      </c>
+      <c r="K74" s="5" t="str">
+        <f>IF('Product Import'!K73="", "", 'Product Import'!K73)</f>
+        <v/>
+      </c>
+      <c r="L74" s="5" t="str">
+        <f>IF('Product Import'!L73="", "", 'Product Import'!L73)</f>
+        <v/>
+      </c>
+      <c r="M74" s="5" t="str">
+        <f>IF('Product Import'!M73="", "", 'Product Import'!M73)</f>
+        <v/>
+      </c>
+      <c r="N74" s="5" t="str">
+        <f>IF('Product Import'!N73="", "", 'Product Import'!N73)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
         <f>'Product Import'!A74</f>
         <v>0</v>
@@ -5953,8 +8019,28 @@
         <f>'Product Import'!I74</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J75" s="5" t="str">
+        <f>IF('Product Import'!J74="", "", 'Product Import'!J74)</f>
+        <v/>
+      </c>
+      <c r="K75" s="5" t="str">
+        <f>IF('Product Import'!K74="", "", 'Product Import'!K74)</f>
+        <v/>
+      </c>
+      <c r="L75" s="5" t="str">
+        <f>IF('Product Import'!L74="", "", 'Product Import'!L74)</f>
+        <v/>
+      </c>
+      <c r="M75" s="5" t="str">
+        <f>IF('Product Import'!M74="", "", 'Product Import'!M74)</f>
+        <v/>
+      </c>
+      <c r="N75" s="5" t="str">
+        <f>IF('Product Import'!N74="", "", 'Product Import'!N74)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <f>'Product Import'!A75</f>
         <v>0</v>
@@ -5991,8 +8077,28 @@
         <f>'Product Import'!I75</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J76" s="5" t="str">
+        <f>IF('Product Import'!J75="", "", 'Product Import'!J75)</f>
+        <v/>
+      </c>
+      <c r="K76" s="5" t="str">
+        <f>IF('Product Import'!K75="", "", 'Product Import'!K75)</f>
+        <v/>
+      </c>
+      <c r="L76" s="5" t="str">
+        <f>IF('Product Import'!L75="", "", 'Product Import'!L75)</f>
+        <v/>
+      </c>
+      <c r="M76" s="5" t="str">
+        <f>IF('Product Import'!M75="", "", 'Product Import'!M75)</f>
+        <v/>
+      </c>
+      <c r="N76" s="5" t="str">
+        <f>IF('Product Import'!N75="", "", 'Product Import'!N75)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
         <f>'Product Import'!A76</f>
         <v>0</v>
@@ -6029,8 +8135,28 @@
         <f>'Product Import'!I76</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J77" s="5" t="str">
+        <f>IF('Product Import'!J76="", "", 'Product Import'!J76)</f>
+        <v/>
+      </c>
+      <c r="K77" s="5" t="str">
+        <f>IF('Product Import'!K76="", "", 'Product Import'!K76)</f>
+        <v/>
+      </c>
+      <c r="L77" s="5" t="str">
+        <f>IF('Product Import'!L76="", "", 'Product Import'!L76)</f>
+        <v/>
+      </c>
+      <c r="M77" s="5" t="str">
+        <f>IF('Product Import'!M76="", "", 'Product Import'!M76)</f>
+        <v/>
+      </c>
+      <c r="N77" s="5" t="str">
+        <f>IF('Product Import'!N76="", "", 'Product Import'!N76)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
         <f>'Product Import'!A77</f>
         <v>0</v>
@@ -6067,8 +8193,28 @@
         <f>'Product Import'!I77</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J78" s="5" t="str">
+        <f>IF('Product Import'!J77="", "", 'Product Import'!J77)</f>
+        <v/>
+      </c>
+      <c r="K78" s="5" t="str">
+        <f>IF('Product Import'!K77="", "", 'Product Import'!K77)</f>
+        <v/>
+      </c>
+      <c r="L78" s="5" t="str">
+        <f>IF('Product Import'!L77="", "", 'Product Import'!L77)</f>
+        <v/>
+      </c>
+      <c r="M78" s="5" t="str">
+        <f>IF('Product Import'!M77="", "", 'Product Import'!M77)</f>
+        <v/>
+      </c>
+      <c r="N78" s="5" t="str">
+        <f>IF('Product Import'!N77="", "", 'Product Import'!N77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
         <f>'Product Import'!A78</f>
         <v>0</v>
@@ -6105,8 +8251,28 @@
         <f>'Product Import'!I78</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J79" s="5" t="str">
+        <f>IF('Product Import'!J78="", "", 'Product Import'!J78)</f>
+        <v/>
+      </c>
+      <c r="K79" s="5" t="str">
+        <f>IF('Product Import'!K78="", "", 'Product Import'!K78)</f>
+        <v/>
+      </c>
+      <c r="L79" s="5" t="str">
+        <f>IF('Product Import'!L78="", "", 'Product Import'!L78)</f>
+        <v/>
+      </c>
+      <c r="M79" s="5" t="str">
+        <f>IF('Product Import'!M78="", "", 'Product Import'!M78)</f>
+        <v/>
+      </c>
+      <c r="N79" s="5" t="str">
+        <f>IF('Product Import'!N78="", "", 'Product Import'!N78)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
         <f>'Product Import'!A79</f>
         <v>0</v>
@@ -6143,8 +8309,28 @@
         <f>'Product Import'!I79</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J80" s="5" t="str">
+        <f>IF('Product Import'!J79="", "", 'Product Import'!J79)</f>
+        <v/>
+      </c>
+      <c r="K80" s="5" t="str">
+        <f>IF('Product Import'!K79="", "", 'Product Import'!K79)</f>
+        <v/>
+      </c>
+      <c r="L80" s="5" t="str">
+        <f>IF('Product Import'!L79="", "", 'Product Import'!L79)</f>
+        <v/>
+      </c>
+      <c r="M80" s="5" t="str">
+        <f>IF('Product Import'!M79="", "", 'Product Import'!M79)</f>
+        <v/>
+      </c>
+      <c r="N80" s="5" t="str">
+        <f>IF('Product Import'!N79="", "", 'Product Import'!N79)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
         <f>'Product Import'!A80</f>
         <v>0</v>
@@ -6181,8 +8367,28 @@
         <f>'Product Import'!I80</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J81" s="5" t="str">
+        <f>IF('Product Import'!J80="", "", 'Product Import'!J80)</f>
+        <v/>
+      </c>
+      <c r="K81" s="5" t="str">
+        <f>IF('Product Import'!K80="", "", 'Product Import'!K80)</f>
+        <v/>
+      </c>
+      <c r="L81" s="5" t="str">
+        <f>IF('Product Import'!L80="", "", 'Product Import'!L80)</f>
+        <v/>
+      </c>
+      <c r="M81" s="5" t="str">
+        <f>IF('Product Import'!M80="", "", 'Product Import'!M80)</f>
+        <v/>
+      </c>
+      <c r="N81" s="5" t="str">
+        <f>IF('Product Import'!N80="", "", 'Product Import'!N80)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
         <f>'Product Import'!A81</f>
         <v>0</v>
@@ -6219,8 +8425,28 @@
         <f>'Product Import'!I81</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J82" s="5" t="str">
+        <f>IF('Product Import'!J81="", "", 'Product Import'!J81)</f>
+        <v/>
+      </c>
+      <c r="K82" s="5" t="str">
+        <f>IF('Product Import'!K81="", "", 'Product Import'!K81)</f>
+        <v/>
+      </c>
+      <c r="L82" s="5" t="str">
+        <f>IF('Product Import'!L81="", "", 'Product Import'!L81)</f>
+        <v/>
+      </c>
+      <c r="M82" s="5" t="str">
+        <f>IF('Product Import'!M81="", "", 'Product Import'!M81)</f>
+        <v/>
+      </c>
+      <c r="N82" s="5" t="str">
+        <f>IF('Product Import'!N81="", "", 'Product Import'!N81)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
         <f>'Product Import'!A82</f>
         <v>0</v>
@@ -6257,8 +8483,28 @@
         <f>'Product Import'!I82</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J83" s="5" t="str">
+        <f>IF('Product Import'!J82="", "", 'Product Import'!J82)</f>
+        <v/>
+      </c>
+      <c r="K83" s="5" t="str">
+        <f>IF('Product Import'!K82="", "", 'Product Import'!K82)</f>
+        <v/>
+      </c>
+      <c r="L83" s="5" t="str">
+        <f>IF('Product Import'!L82="", "", 'Product Import'!L82)</f>
+        <v/>
+      </c>
+      <c r="M83" s="5" t="str">
+        <f>IF('Product Import'!M82="", "", 'Product Import'!M82)</f>
+        <v/>
+      </c>
+      <c r="N83" s="5" t="str">
+        <f>IF('Product Import'!N82="", "", 'Product Import'!N82)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
         <f>'Product Import'!A83</f>
         <v>0</v>
@@ -6295,8 +8541,28 @@
         <f>'Product Import'!I83</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J84" s="5" t="str">
+        <f>IF('Product Import'!J83="", "", 'Product Import'!J83)</f>
+        <v/>
+      </c>
+      <c r="K84" s="5" t="str">
+        <f>IF('Product Import'!K83="", "", 'Product Import'!K83)</f>
+        <v/>
+      </c>
+      <c r="L84" s="5" t="str">
+        <f>IF('Product Import'!L83="", "", 'Product Import'!L83)</f>
+        <v/>
+      </c>
+      <c r="M84" s="5" t="str">
+        <f>IF('Product Import'!M83="", "", 'Product Import'!M83)</f>
+        <v/>
+      </c>
+      <c r="N84" s="5" t="str">
+        <f>IF('Product Import'!N83="", "", 'Product Import'!N83)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
         <f>'Product Import'!A84</f>
         <v>0</v>
@@ -6333,8 +8599,28 @@
         <f>'Product Import'!I84</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J85" s="5" t="str">
+        <f>IF('Product Import'!J84="", "", 'Product Import'!J84)</f>
+        <v/>
+      </c>
+      <c r="K85" s="5" t="str">
+        <f>IF('Product Import'!K84="", "", 'Product Import'!K84)</f>
+        <v/>
+      </c>
+      <c r="L85" s="5" t="str">
+        <f>IF('Product Import'!L84="", "", 'Product Import'!L84)</f>
+        <v/>
+      </c>
+      <c r="M85" s="5" t="str">
+        <f>IF('Product Import'!M84="", "", 'Product Import'!M84)</f>
+        <v/>
+      </c>
+      <c r="N85" s="5" t="str">
+        <f>IF('Product Import'!N84="", "", 'Product Import'!N84)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
         <f>'Product Import'!A85</f>
         <v>0</v>
@@ -6371,8 +8657,28 @@
         <f>'Product Import'!I85</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J86" s="5" t="str">
+        <f>IF('Product Import'!J85="", "", 'Product Import'!J85)</f>
+        <v/>
+      </c>
+      <c r="K86" s="5" t="str">
+        <f>IF('Product Import'!K85="", "", 'Product Import'!K85)</f>
+        <v/>
+      </c>
+      <c r="L86" s="5" t="str">
+        <f>IF('Product Import'!L85="", "", 'Product Import'!L85)</f>
+        <v/>
+      </c>
+      <c r="M86" s="5" t="str">
+        <f>IF('Product Import'!M85="", "", 'Product Import'!M85)</f>
+        <v/>
+      </c>
+      <c r="N86" s="5" t="str">
+        <f>IF('Product Import'!N85="", "", 'Product Import'!N85)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
         <f>'Product Import'!A86</f>
         <v>0</v>
@@ -6409,8 +8715,28 @@
         <f>'Product Import'!I86</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J87" s="5" t="str">
+        <f>IF('Product Import'!J86="", "", 'Product Import'!J86)</f>
+        <v/>
+      </c>
+      <c r="K87" s="5" t="str">
+        <f>IF('Product Import'!K86="", "", 'Product Import'!K86)</f>
+        <v/>
+      </c>
+      <c r="L87" s="5" t="str">
+        <f>IF('Product Import'!L86="", "", 'Product Import'!L86)</f>
+        <v/>
+      </c>
+      <c r="M87" s="5" t="str">
+        <f>IF('Product Import'!M86="", "", 'Product Import'!M86)</f>
+        <v/>
+      </c>
+      <c r="N87" s="5" t="str">
+        <f>IF('Product Import'!N86="", "", 'Product Import'!N86)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="5">
         <f>'Product Import'!A87</f>
         <v>0</v>
@@ -6447,8 +8773,28 @@
         <f>'Product Import'!I87</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J88" s="5" t="str">
+        <f>IF('Product Import'!J87="", "", 'Product Import'!J87)</f>
+        <v/>
+      </c>
+      <c r="K88" s="5" t="str">
+        <f>IF('Product Import'!K87="", "", 'Product Import'!K87)</f>
+        <v/>
+      </c>
+      <c r="L88" s="5" t="str">
+        <f>IF('Product Import'!L87="", "", 'Product Import'!L87)</f>
+        <v/>
+      </c>
+      <c r="M88" s="5" t="str">
+        <f>IF('Product Import'!M87="", "", 'Product Import'!M87)</f>
+        <v/>
+      </c>
+      <c r="N88" s="5" t="str">
+        <f>IF('Product Import'!N87="", "", 'Product Import'!N87)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
         <f>'Product Import'!A88</f>
         <v>0</v>
@@ -6485,8 +8831,28 @@
         <f>'Product Import'!I88</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J89" s="5" t="str">
+        <f>IF('Product Import'!J88="", "", 'Product Import'!J88)</f>
+        <v/>
+      </c>
+      <c r="K89" s="5" t="str">
+        <f>IF('Product Import'!K88="", "", 'Product Import'!K88)</f>
+        <v/>
+      </c>
+      <c r="L89" s="5" t="str">
+        <f>IF('Product Import'!L88="", "", 'Product Import'!L88)</f>
+        <v/>
+      </c>
+      <c r="M89" s="5" t="str">
+        <f>IF('Product Import'!M88="", "", 'Product Import'!M88)</f>
+        <v/>
+      </c>
+      <c r="N89" s="5" t="str">
+        <f>IF('Product Import'!N88="", "", 'Product Import'!N88)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
         <f>'Product Import'!A89</f>
         <v>0</v>
@@ -6523,8 +8889,28 @@
         <f>'Product Import'!I89</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J90" s="5" t="str">
+        <f>IF('Product Import'!J89="", "", 'Product Import'!J89)</f>
+        <v/>
+      </c>
+      <c r="K90" s="5" t="str">
+        <f>IF('Product Import'!K89="", "", 'Product Import'!K89)</f>
+        <v/>
+      </c>
+      <c r="L90" s="5" t="str">
+        <f>IF('Product Import'!L89="", "", 'Product Import'!L89)</f>
+        <v/>
+      </c>
+      <c r="M90" s="5" t="str">
+        <f>IF('Product Import'!M89="", "", 'Product Import'!M89)</f>
+        <v/>
+      </c>
+      <c r="N90" s="5" t="str">
+        <f>IF('Product Import'!N89="", "", 'Product Import'!N89)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="5">
         <f>'Product Import'!A90</f>
         <v>0</v>
@@ -6561,8 +8947,28 @@
         <f>'Product Import'!I90</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J91" s="5" t="str">
+        <f>IF('Product Import'!J90="", "", 'Product Import'!J90)</f>
+        <v/>
+      </c>
+      <c r="K91" s="5" t="str">
+        <f>IF('Product Import'!K90="", "", 'Product Import'!K90)</f>
+        <v/>
+      </c>
+      <c r="L91" s="5" t="str">
+        <f>IF('Product Import'!L90="", "", 'Product Import'!L90)</f>
+        <v/>
+      </c>
+      <c r="M91" s="5" t="str">
+        <f>IF('Product Import'!M90="", "", 'Product Import'!M90)</f>
+        <v/>
+      </c>
+      <c r="N91" s="5" t="str">
+        <f>IF('Product Import'!N90="", "", 'Product Import'!N90)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
         <f>'Product Import'!A91</f>
         <v>0</v>
@@ -6599,8 +9005,28 @@
         <f>'Product Import'!I91</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J92" s="5" t="str">
+        <f>IF('Product Import'!J91="", "", 'Product Import'!J91)</f>
+        <v/>
+      </c>
+      <c r="K92" s="5" t="str">
+        <f>IF('Product Import'!K91="", "", 'Product Import'!K91)</f>
+        <v/>
+      </c>
+      <c r="L92" s="5" t="str">
+        <f>IF('Product Import'!L91="", "", 'Product Import'!L91)</f>
+        <v/>
+      </c>
+      <c r="M92" s="5" t="str">
+        <f>IF('Product Import'!M91="", "", 'Product Import'!M91)</f>
+        <v/>
+      </c>
+      <c r="N92" s="5" t="str">
+        <f>IF('Product Import'!N91="", "", 'Product Import'!N91)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
         <f>'Product Import'!A92</f>
         <v>0</v>
@@ -6637,8 +9063,28 @@
         <f>'Product Import'!I92</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J93" s="5" t="str">
+        <f>IF('Product Import'!J92="", "", 'Product Import'!J92)</f>
+        <v/>
+      </c>
+      <c r="K93" s="5" t="str">
+        <f>IF('Product Import'!K92="", "", 'Product Import'!K92)</f>
+        <v/>
+      </c>
+      <c r="L93" s="5" t="str">
+        <f>IF('Product Import'!L92="", "", 'Product Import'!L92)</f>
+        <v/>
+      </c>
+      <c r="M93" s="5" t="str">
+        <f>IF('Product Import'!M92="", "", 'Product Import'!M92)</f>
+        <v/>
+      </c>
+      <c r="N93" s="5" t="str">
+        <f>IF('Product Import'!N92="", "", 'Product Import'!N92)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="5">
         <f>'Product Import'!A93</f>
         <v>0</v>
@@ -6675,8 +9121,28 @@
         <f>'Product Import'!I93</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J94" s="5" t="str">
+        <f>IF('Product Import'!J93="", "", 'Product Import'!J93)</f>
+        <v/>
+      </c>
+      <c r="K94" s="5" t="str">
+        <f>IF('Product Import'!K93="", "", 'Product Import'!K93)</f>
+        <v/>
+      </c>
+      <c r="L94" s="5" t="str">
+        <f>IF('Product Import'!L93="", "", 'Product Import'!L93)</f>
+        <v/>
+      </c>
+      <c r="M94" s="5" t="str">
+        <f>IF('Product Import'!M93="", "", 'Product Import'!M93)</f>
+        <v/>
+      </c>
+      <c r="N94" s="5" t="str">
+        <f>IF('Product Import'!N93="", "", 'Product Import'!N93)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="5">
         <f>'Product Import'!A94</f>
         <v>0</v>
@@ -6713,8 +9179,28 @@
         <f>'Product Import'!I94</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J95" s="5" t="str">
+        <f>IF('Product Import'!J94="", "", 'Product Import'!J94)</f>
+        <v/>
+      </c>
+      <c r="K95" s="5" t="str">
+        <f>IF('Product Import'!K94="", "", 'Product Import'!K94)</f>
+        <v/>
+      </c>
+      <c r="L95" s="5" t="str">
+        <f>IF('Product Import'!L94="", "", 'Product Import'!L94)</f>
+        <v/>
+      </c>
+      <c r="M95" s="5" t="str">
+        <f>IF('Product Import'!M94="", "", 'Product Import'!M94)</f>
+        <v/>
+      </c>
+      <c r="N95" s="5" t="str">
+        <f>IF('Product Import'!N94="", "", 'Product Import'!N94)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="5">
         <f>'Product Import'!A95</f>
         <v>0</v>
@@ -6751,8 +9237,28 @@
         <f>'Product Import'!I95</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J96" s="5" t="str">
+        <f>IF('Product Import'!J95="", "", 'Product Import'!J95)</f>
+        <v/>
+      </c>
+      <c r="K96" s="5" t="str">
+        <f>IF('Product Import'!K95="", "", 'Product Import'!K95)</f>
+        <v/>
+      </c>
+      <c r="L96" s="5" t="str">
+        <f>IF('Product Import'!L95="", "", 'Product Import'!L95)</f>
+        <v/>
+      </c>
+      <c r="M96" s="5" t="str">
+        <f>IF('Product Import'!M95="", "", 'Product Import'!M95)</f>
+        <v/>
+      </c>
+      <c r="N96" s="5" t="str">
+        <f>IF('Product Import'!N95="", "", 'Product Import'!N95)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="5">
         <f>'Product Import'!A96</f>
         <v>0</v>
@@ -6789,8 +9295,28 @@
         <f>'Product Import'!I96</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J97" s="5" t="str">
+        <f>IF('Product Import'!J96="", "", 'Product Import'!J96)</f>
+        <v/>
+      </c>
+      <c r="K97" s="5" t="str">
+        <f>IF('Product Import'!K96="", "", 'Product Import'!K96)</f>
+        <v/>
+      </c>
+      <c r="L97" s="5" t="str">
+        <f>IF('Product Import'!L96="", "", 'Product Import'!L96)</f>
+        <v/>
+      </c>
+      <c r="M97" s="5" t="str">
+        <f>IF('Product Import'!M96="", "", 'Product Import'!M96)</f>
+        <v/>
+      </c>
+      <c r="N97" s="5" t="str">
+        <f>IF('Product Import'!N96="", "", 'Product Import'!N96)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="5">
         <f>'Product Import'!A97</f>
         <v>0</v>
@@ -6827,8 +9353,28 @@
         <f>'Product Import'!I97</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J98" s="5" t="str">
+        <f>IF('Product Import'!J97="", "", 'Product Import'!J97)</f>
+        <v/>
+      </c>
+      <c r="K98" s="5" t="str">
+        <f>IF('Product Import'!K97="", "", 'Product Import'!K97)</f>
+        <v/>
+      </c>
+      <c r="L98" s="5" t="str">
+        <f>IF('Product Import'!L97="", "", 'Product Import'!L97)</f>
+        <v/>
+      </c>
+      <c r="M98" s="5" t="str">
+        <f>IF('Product Import'!M97="", "", 'Product Import'!M97)</f>
+        <v/>
+      </c>
+      <c r="N98" s="5" t="str">
+        <f>IF('Product Import'!N97="", "", 'Product Import'!N97)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
         <f>'Product Import'!A98</f>
         <v>0</v>
@@ -6865,8 +9411,28 @@
         <f>'Product Import'!I98</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J99" s="5" t="str">
+        <f>IF('Product Import'!J98="", "", 'Product Import'!J98)</f>
+        <v/>
+      </c>
+      <c r="K99" s="5" t="str">
+        <f>IF('Product Import'!K98="", "", 'Product Import'!K98)</f>
+        <v/>
+      </c>
+      <c r="L99" s="5" t="str">
+        <f>IF('Product Import'!L98="", "", 'Product Import'!L98)</f>
+        <v/>
+      </c>
+      <c r="M99" s="5" t="str">
+        <f>IF('Product Import'!M98="", "", 'Product Import'!M98)</f>
+        <v/>
+      </c>
+      <c r="N99" s="5" t="str">
+        <f>IF('Product Import'!N98="", "", 'Product Import'!N98)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="5">
         <f>'Product Import'!A99</f>
         <v>0</v>
@@ -6903,8 +9469,28 @@
         <f>'Product Import'!I99</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J100" s="5" t="str">
+        <f>IF('Product Import'!J99="", "", 'Product Import'!J99)</f>
+        <v/>
+      </c>
+      <c r="K100" s="5" t="str">
+        <f>IF('Product Import'!K99="", "", 'Product Import'!K99)</f>
+        <v/>
+      </c>
+      <c r="L100" s="5" t="str">
+        <f>IF('Product Import'!L99="", "", 'Product Import'!L99)</f>
+        <v/>
+      </c>
+      <c r="M100" s="5" t="str">
+        <f>IF('Product Import'!M99="", "", 'Product Import'!M99)</f>
+        <v/>
+      </c>
+      <c r="N100" s="5" t="str">
+        <f>IF('Product Import'!N99="", "", 'Product Import'!N99)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
         <f>'Product Import'!A100</f>
         <v>0</v>
@@ -6941,8 +9527,28 @@
         <f>'Product Import'!I100</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J101" s="5" t="str">
+        <f>IF('Product Import'!J100="", "", 'Product Import'!J100)</f>
+        <v/>
+      </c>
+      <c r="K101" s="5" t="str">
+        <f>IF('Product Import'!K100="", "", 'Product Import'!K100)</f>
+        <v/>
+      </c>
+      <c r="L101" s="5" t="str">
+        <f>IF('Product Import'!L100="", "", 'Product Import'!L100)</f>
+        <v/>
+      </c>
+      <c r="M101" s="5" t="str">
+        <f>IF('Product Import'!M100="", "", 'Product Import'!M100)</f>
+        <v/>
+      </c>
+      <c r="N101" s="5" t="str">
+        <f>IF('Product Import'!N100="", "", 'Product Import'!N100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" s="5">
         <f>'Product Import'!A101</f>
         <v>0</v>
@@ -6978,6 +9584,26 @@
       <c r="I102" s="5">
         <f>'Product Import'!I101</f>
         <v>0</v>
+      </c>
+      <c r="J102" s="5" t="str">
+        <f>IF('Product Import'!J101="", "", 'Product Import'!J101)</f>
+        <v/>
+      </c>
+      <c r="K102" s="5" t="str">
+        <f>IF('Product Import'!K101="", "", 'Product Import'!K101)</f>
+        <v/>
+      </c>
+      <c r="L102" s="5" t="str">
+        <f>IF('Product Import'!L101="", "", 'Product Import'!L101)</f>
+        <v/>
+      </c>
+      <c r="M102" s="5" t="str">
+        <f>IF('Product Import'!M101="", "", 'Product Import'!M101)</f>
+        <v/>
+      </c>
+      <c r="N102" s="5" t="str">
+        <f>IF('Product Import'!N101="", "", 'Product Import'!N101)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
